--- a/onsets_edit.xlsx
+++ b/onsets_edit.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/brandonwoosnyder/Dropbox/docs-d/00_UCI_2025-2026/02_UCI_Winter_2026/Independent Study Rajna - Music 299/Constrained_PhoneGuide_Score/ScreenTimeScore/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{305A3D76-5BEF-CE42-A467-C8D6CDCBFAA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CADD9A4-F67A-8A4F-8662-F187C0B00684}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="180" yWindow="840" windowWidth="30060" windowHeight="17180" xr2:uid="{656903FE-55D6-334E-8317-D02588440573}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="506" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="511" uniqueCount="68">
   <si>
     <t>onset_ms_1</t>
   </si>
@@ -234,6 +234,9 @@
   </si>
   <si>
     <t>IS THIS VALUE BELOW CORRECT???</t>
+  </si>
+  <si>
+    <t>bacon01bright</t>
   </si>
 </sst>
 </file>
@@ -1094,7 +1097,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E707C8EF-5282-2B42-BB2D-C2C257FF5AA3}">
-  <dimension ref="A1:S84"/>
+  <dimension ref="A1:S85"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="26.6640625" bestFit="1" customWidth="1"/>
@@ -1677,1030 +1680,1029 @@
         <v>64</v>
       </c>
       <c r="P12">
+        <f>P2+1</f>
         <v>2</v>
       </c>
       <c r="Q12">
-        <v>60</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A13">
         <f>A12+($Q12*1000)</f>
-        <v>70000</v>
+        <v>30000</v>
       </c>
       <c r="B13" t="s">
-        <v>19</v>
-      </c>
-      <c r="C13" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D13">
         <f>D12+($Q12*1000)</f>
-        <v>70000</v>
+        <v>30000</v>
       </c>
       <c r="E13" t="s">
-        <v>19</v>
-      </c>
-      <c r="F13" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G13">
         <f>G12+($Q12*1000)</f>
-        <v>70000</v>
+        <v>30000</v>
       </c>
       <c r="H13" t="s">
-        <v>19</v>
-      </c>
-      <c r="I13" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="J13">
         <f>J12+($Q12*1000)</f>
-        <v>70000</v>
+        <v>30000</v>
       </c>
       <c r="K13" t="s">
-        <v>19</v>
-      </c>
-      <c r="L13" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="M13">
         <f>M12+($Q12*1000)</f>
-        <v>70000</v>
+        <v>30000</v>
       </c>
       <c r="N13" t="s">
-        <v>19</v>
-      </c>
-      <c r="O13" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="P13">
+        <f>P12+1</f>
         <v>3</v>
       </c>
       <c r="Q13">
-        <v>6</v>
+        <v>20</v>
       </c>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A14">
         <f>A13+($Q13*1000)</f>
-        <v>76000</v>
+        <v>50000</v>
       </c>
       <c r="B14" t="s">
         <v>19</v>
       </c>
       <c r="C14" t="s">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="D14">
         <f>D13+($Q13*1000)</f>
-        <v>76000</v>
+        <v>50000</v>
       </c>
       <c r="E14" t="s">
         <v>19</v>
       </c>
       <c r="F14" t="s">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="G14">
         <f>G13+($Q13*1000)</f>
-        <v>76000</v>
+        <v>50000</v>
       </c>
       <c r="H14" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="I14" t="s">
-        <v>32</v>
+        <v>65</v>
       </c>
       <c r="J14">
         <f>J13+($Q13*1000)</f>
-        <v>76000</v>
+        <v>50000</v>
       </c>
       <c r="K14" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="L14" t="s">
-        <v>33</v>
+        <v>65</v>
       </c>
       <c r="M14">
         <f>M13+($Q13*1000)</f>
-        <v>76000</v>
+        <v>50000</v>
       </c>
       <c r="N14" t="s">
         <v>19</v>
       </c>
       <c r="O14" t="s">
+        <v>65</v>
+      </c>
+      <c r="P14">
+        <f>P13+1</f>
+        <v>4</v>
+      </c>
+      <c r="Q14">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A15">
+        <f>A14+($Q14*1000)</f>
+        <v>56000</v>
+      </c>
+      <c r="B15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C15" t="s">
         <v>30</v>
       </c>
-      <c r="P14">
-        <v>4</v>
-      </c>
-      <c r="Q14">
+      <c r="D15">
+        <f>D14+($Q14*1000)</f>
+        <v>56000</v>
+      </c>
+      <c r="E15" t="s">
+        <v>19</v>
+      </c>
+      <c r="F15" t="s">
+        <v>30</v>
+      </c>
+      <c r="G15">
+        <f>G14+($Q14*1000)</f>
+        <v>56000</v>
+      </c>
+      <c r="H15" t="s">
+        <v>31</v>
+      </c>
+      <c r="I15" t="s">
+        <v>32</v>
+      </c>
+      <c r="J15">
+        <f>J14+($Q14*1000)</f>
+        <v>56000</v>
+      </c>
+      <c r="K15" t="s">
+        <v>31</v>
+      </c>
+      <c r="L15" t="s">
+        <v>33</v>
+      </c>
+      <c r="M15">
+        <f>M14+($Q14*1000)</f>
+        <v>56000</v>
+      </c>
+      <c r="N15" t="s">
+        <v>19</v>
+      </c>
+      <c r="O15" t="s">
+        <v>30</v>
+      </c>
+      <c r="P15">
+        <f>P14+1</f>
+        <v>5</v>
+      </c>
+      <c r="Q15">
         <v>24</v>
-      </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="G15">
-        <f t="shared" ref="G15:G20" si="0">G14+($S$2)</f>
-        <v>80000</v>
-      </c>
-      <c r="H15" t="s">
-        <v>19</v>
-      </c>
-      <c r="I15" t="s">
-        <v>34</v>
-      </c>
-      <c r="J15">
-        <f t="shared" ref="J15:J26" si="1">J14+($S$2*(1+$R$2))</f>
-        <v>80050</v>
-      </c>
-      <c r="K15" t="s">
-        <v>19</v>
-      </c>
-      <c r="L15" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="G16">
-        <f t="shared" si="0"/>
-        <v>84000</v>
+        <f t="shared" ref="G16:G21" si="0">G15+($S$2)</f>
+        <v>60000</v>
       </c>
       <c r="H16" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="I16" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J16">
-        <f t="shared" si="1"/>
-        <v>84100</v>
+        <f t="shared" ref="J16:J27" si="1">J15+($S$2*(1+$R$2))</f>
+        <v>60050</v>
       </c>
       <c r="K16" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="L16" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.2">
       <c r="G17">
         <f t="shared" si="0"/>
-        <v>88000</v>
+        <v>64000</v>
       </c>
       <c r="H17" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="I17" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="J17">
         <f t="shared" si="1"/>
-        <v>88150</v>
+        <v>64100</v>
       </c>
       <c r="K17" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="L17" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.2">
       <c r="G18">
         <f t="shared" si="0"/>
-        <v>92000</v>
+        <v>68000</v>
       </c>
       <c r="H18" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="I18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J18">
         <f t="shared" si="1"/>
-        <v>92200</v>
+        <v>68150</v>
       </c>
       <c r="K18" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="L18" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.2">
       <c r="G19">
         <f t="shared" si="0"/>
-        <v>96000</v>
+        <v>72000</v>
       </c>
       <c r="H19" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="I19" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="J19">
         <f t="shared" si="1"/>
-        <v>96250</v>
+        <v>72200</v>
       </c>
       <c r="K19" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="L19" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A20">
-        <f>A14+($Q14*1000)</f>
-        <v>100000</v>
-      </c>
-      <c r="B20" t="s">
-        <v>19</v>
-      </c>
-      <c r="C20" t="s">
-        <v>36</v>
-      </c>
-      <c r="D20">
-        <f>D14+($Q14*1000)</f>
-        <v>100000</v>
-      </c>
-      <c r="E20" t="s">
-        <v>19</v>
-      </c>
-      <c r="F20" t="s">
-        <v>36</v>
-      </c>
       <c r="G20">
         <f t="shared" si="0"/>
-        <v>100000</v>
+        <v>76000</v>
       </c>
       <c r="H20" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="I20" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J20">
         <f t="shared" si="1"/>
-        <v>100300</v>
+        <v>76250</v>
       </c>
       <c r="K20" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="L20" t="s">
-        <v>33</v>
-      </c>
-      <c r="M20">
-        <f>M14+($Q14*1000)</f>
-        <v>100000</v>
-      </c>
-      <c r="N20" t="s">
-        <v>19</v>
-      </c>
-      <c r="O20" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A21">
+        <f>A15+($Q15*1000)</f>
+        <v>80000</v>
+      </c>
+      <c r="B21" t="s">
+        <v>19</v>
+      </c>
+      <c r="C21" t="s">
         <v>36</v>
       </c>
-      <c r="P20">
-        <v>5</v>
-      </c>
-      <c r="Q20">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="D21">
+        <f>D15+($Q15*1000)</f>
+        <v>80000</v>
+      </c>
+      <c r="E21" t="s">
+        <v>19</v>
+      </c>
+      <c r="F21" t="s">
+        <v>36</v>
+      </c>
       <c r="G21">
-        <f t="shared" ref="G21:G39" si="2">G20+($S$2)</f>
-        <v>104000</v>
+        <f t="shared" si="0"/>
+        <v>80000</v>
       </c>
       <c r="H21" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="I21" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="J21">
         <f t="shared" si="1"/>
-        <v>104350</v>
+        <v>80300</v>
       </c>
       <c r="K21" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="L21" t="s">
-        <v>35</v>
+        <v>33</v>
+      </c>
+      <c r="M21">
+        <f>M15+($Q15*1000)</f>
+        <v>80000</v>
+      </c>
+      <c r="N21" t="s">
+        <v>19</v>
+      </c>
+      <c r="O21" t="s">
+        <v>36</v>
+      </c>
+      <c r="P21">
+        <f>P15+1</f>
+        <v>6</v>
+      </c>
+      <c r="Q21">
+        <v>28</v>
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.2">
       <c r="G22">
-        <f t="shared" si="2"/>
-        <v>108000</v>
+        <f t="shared" ref="G22:G40" si="2">G21+($S$2)</f>
+        <v>84000</v>
       </c>
       <c r="H22" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="I22" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J22">
         <f t="shared" si="1"/>
-        <v>108400</v>
+        <v>84350</v>
       </c>
       <c r="K22" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="L22" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.2">
       <c r="G23">
         <f t="shared" si="2"/>
-        <v>112000</v>
+        <v>88000</v>
       </c>
       <c r="H23" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="I23" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="J23">
         <f t="shared" si="1"/>
-        <v>112450</v>
+        <v>88400</v>
       </c>
       <c r="K23" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="L23" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.2">
       <c r="G24">
         <f t="shared" si="2"/>
-        <v>116000</v>
+        <v>92000</v>
       </c>
       <c r="H24" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="I24" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J24">
         <f t="shared" si="1"/>
-        <v>116500</v>
+        <v>92450</v>
       </c>
       <c r="K24" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="L24" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.2">
       <c r="G25">
         <f t="shared" si="2"/>
-        <v>120000</v>
+        <v>96000</v>
       </c>
       <c r="H25" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="I25" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="J25">
         <f t="shared" si="1"/>
-        <v>120550</v>
+        <v>96500</v>
       </c>
       <c r="K25" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="L25" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.2">
       <c r="G26">
         <f t="shared" si="2"/>
-        <v>124000</v>
+        <v>100000</v>
       </c>
       <c r="H26" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="I26" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J26">
         <f t="shared" si="1"/>
-        <v>124600</v>
+        <v>100550</v>
       </c>
       <c r="K26" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="L26" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A27">
-        <f>A20+($Q20*1000)</f>
-        <v>128000</v>
-      </c>
-      <c r="B27" t="s">
-        <v>19</v>
-      </c>
-      <c r="C27" t="s">
-        <v>36</v>
-      </c>
-      <c r="D27">
-        <f>D20+($Q20*1000)</f>
-        <v>128000</v>
-      </c>
-      <c r="E27" t="s">
-        <v>19</v>
-      </c>
-      <c r="F27" t="s">
-        <v>36</v>
-      </c>
       <c r="G27">
         <f t="shared" si="2"/>
-        <v>128000</v>
+        <v>104000</v>
       </c>
       <c r="H27" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="I27" t="s">
-        <v>34</v>
-      </c>
-      <c r="M27">
-        <f>M20+($Q20*1000)</f>
-        <v>128000</v>
-      </c>
-      <c r="N27" t="s">
-        <v>19</v>
-      </c>
-      <c r="O27" t="s">
+        <v>32</v>
+      </c>
+      <c r="J27">
+        <f t="shared" si="1"/>
+        <v>104600</v>
+      </c>
+      <c r="K27" t="s">
+        <v>31</v>
+      </c>
+      <c r="L27" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A28">
+        <f>A21+($Q21*1000)</f>
+        <v>108000</v>
+      </c>
+      <c r="B28" t="s">
+        <v>19</v>
+      </c>
+      <c r="C28" t="s">
         <v>36</v>
       </c>
-      <c r="P27">
-        <v>6</v>
-      </c>
-      <c r="Q27">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="D28">
+        <f>D21+($Q21*1000)</f>
+        <v>108000</v>
+      </c>
+      <c r="E28" t="s">
+        <v>19</v>
+      </c>
+      <c r="F28" t="s">
+        <v>36</v>
+      </c>
       <c r="G28">
         <f t="shared" si="2"/>
-        <v>132000</v>
+        <v>108000</v>
       </c>
       <c r="H28" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="I28" t="s">
-        <v>32</v>
+        <v>34</v>
+      </c>
+      <c r="M28">
+        <f>M21+($Q21*1000)</f>
+        <v>108000</v>
+      </c>
+      <c r="N28" t="s">
+        <v>19</v>
+      </c>
+      <c r="O28" t="s">
+        <v>36</v>
+      </c>
+      <c r="P28">
+        <f>P21+1</f>
+        <v>7</v>
+      </c>
+      <c r="Q28">
+        <v>28</v>
       </c>
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.2">
       <c r="G29">
         <f t="shared" si="2"/>
-        <v>136000</v>
+        <v>112000</v>
       </c>
       <c r="H29" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="I29" t="s">
-        <v>34</v>
-      </c>
-      <c r="J29">
-        <f>J26+(11000)</f>
-        <v>135600</v>
-      </c>
-      <c r="K29" t="s">
-        <v>19</v>
-      </c>
-      <c r="L29" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.2">
       <c r="G30">
         <f t="shared" si="2"/>
-        <v>140000</v>
+        <v>116000</v>
       </c>
       <c r="H30" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="I30" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J30">
-        <f>J29+2000</f>
-        <v>137600</v>
+        <f>J27+(11000)</f>
+        <v>115600</v>
       </c>
       <c r="K30" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="L30" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.2">
       <c r="G31">
         <f t="shared" si="2"/>
-        <v>144000</v>
+        <v>120000</v>
       </c>
       <c r="H31" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="I31" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="J31">
-        <f>J30+4000</f>
-        <v>141600</v>
+        <f>J30+2000</f>
+        <v>117600</v>
       </c>
       <c r="K31" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="L31" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.2">
       <c r="G32">
         <f t="shared" si="2"/>
-        <v>148000</v>
+        <v>124000</v>
       </c>
       <c r="H32" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="I32" t="s">
-        <v>32</v>
+        <v>34</v>
+      </c>
+      <c r="J32">
+        <f>J31+4000</f>
+        <v>121600</v>
+      </c>
+      <c r="K32" t="s">
+        <v>19</v>
+      </c>
+      <c r="L32" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.2">
       <c r="G33">
         <f t="shared" si="2"/>
-        <v>152000</v>
+        <v>128000</v>
       </c>
       <c r="H33" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="I33" t="s">
-        <v>34</v>
-      </c>
-      <c r="J33">
-        <f>J31+11000</f>
-        <v>152600</v>
-      </c>
-      <c r="K33" t="s">
-        <v>19</v>
-      </c>
-      <c r="L33" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="34" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A34">
-        <f>A27+($Q27*1000)</f>
-        <v>156000</v>
-      </c>
-      <c r="B34" t="s">
-        <v>19</v>
-      </c>
-      <c r="C34" t="s">
-        <v>40</v>
-      </c>
-      <c r="D34">
-        <f>D27+($Q27*1000)</f>
-        <v>156000</v>
-      </c>
-      <c r="E34" t="s">
-        <v>19</v>
-      </c>
-      <c r="F34" t="s">
-        <v>40</v>
-      </c>
       <c r="G34">
         <f t="shared" si="2"/>
-        <v>156000</v>
+        <v>132000</v>
       </c>
       <c r="H34" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="I34" t="s">
-        <v>32</v>
-      </c>
-      <c r="M34">
-        <f>M27+($Q27*1000)</f>
-        <v>156000</v>
-      </c>
-      <c r="N34" t="s">
-        <v>19</v>
-      </c>
-      <c r="O34" t="s">
+        <v>34</v>
+      </c>
+      <c r="J34">
+        <f>J32+11000</f>
+        <v>132600</v>
+      </c>
+      <c r="K34" t="s">
+        <v>19</v>
+      </c>
+      <c r="L34" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A35">
+        <f>A28+($Q28*1000)</f>
+        <v>136000</v>
+      </c>
+      <c r="B35" t="s">
+        <v>19</v>
+      </c>
+      <c r="C35" t="s">
         <v>40</v>
       </c>
-      <c r="P34">
-        <v>7</v>
-      </c>
-      <c r="Q34">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="35" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="D35">
+        <f>D28+($Q28*1000)</f>
+        <v>136000</v>
+      </c>
+      <c r="E35" t="s">
+        <v>19</v>
+      </c>
+      <c r="F35" t="s">
+        <v>40</v>
+      </c>
       <c r="G35">
         <f t="shared" si="2"/>
-        <v>160000</v>
+        <v>136000</v>
       </c>
       <c r="H35" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="I35" t="s">
-        <v>34</v>
-      </c>
-      <c r="J35">
-        <f>G35</f>
-        <v>160000</v>
-      </c>
-      <c r="K35" t="s">
-        <v>31</v>
-      </c>
-      <c r="L35" t="s">
         <v>32</v>
+      </c>
+      <c r="M35">
+        <f>M28+($Q28*1000)</f>
+        <v>136000</v>
+      </c>
+      <c r="N35" t="s">
+        <v>19</v>
+      </c>
+      <c r="O35" t="s">
+        <v>40</v>
+      </c>
+      <c r="P35">
+        <f>P28+1</f>
+        <v>8</v>
+      </c>
+      <c r="Q35">
+        <v>12</v>
       </c>
     </row>
     <row r="36" spans="1:18" x14ac:dyDescent="0.2">
       <c r="G36">
-        <f>G35+($S$2)</f>
-        <v>164000</v>
+        <f t="shared" si="2"/>
+        <v>140000</v>
       </c>
       <c r="H36" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="I36" t="s">
+        <v>34</v>
+      </c>
+      <c r="J36">
+        <f>G36</f>
+        <v>140000</v>
+      </c>
+      <c r="K36" t="s">
+        <v>31</v>
+      </c>
+      <c r="L36" t="s">
         <v>32</v>
-      </c>
-      <c r="J36">
-        <f>J35+($S$2)</f>
-        <v>164000</v>
-      </c>
-      <c r="K36" t="s">
-        <v>19</v>
-      </c>
-      <c r="L36" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="37" spans="1:18" x14ac:dyDescent="0.2">
       <c r="G37">
         <f>G36+($S$2)</f>
-        <v>168000</v>
+        <v>144000</v>
       </c>
       <c r="H37" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="I37" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="J37">
         <f>J36+($S$2)</f>
-        <v>168000</v>
+        <v>144000</v>
       </c>
       <c r="K37" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="L37" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="38" spans="1:18" x14ac:dyDescent="0.2">
       <c r="G38">
-        <f t="shared" si="2"/>
-        <v>172000</v>
+        <f>G37+($S$2)</f>
+        <v>148000</v>
       </c>
       <c r="H38" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="I38" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J38">
         <f>J37+($S$2)</f>
-        <v>172000</v>
+        <v>148000</v>
       </c>
       <c r="K38" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="L38" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="39" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A39">
-        <f>A34+($Q34*1000)</f>
-        <v>168000</v>
-      </c>
-      <c r="B39" t="s">
-        <v>19</v>
-      </c>
-      <c r="C39" t="s">
-        <v>41</v>
-      </c>
-      <c r="D39">
-        <f>D34+($Q34*1000)</f>
-        <v>168000</v>
-      </c>
-      <c r="E39" t="s">
-        <v>19</v>
-      </c>
-      <c r="F39" t="s">
-        <v>41</v>
-      </c>
       <c r="G39">
         <f t="shared" si="2"/>
-        <v>176000</v>
+        <v>152000</v>
       </c>
       <c r="H39" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="I39" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="J39">
         <f>J38+($S$2)</f>
-        <v>176000</v>
+        <v>152000</v>
       </c>
       <c r="K39" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="L39" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="40" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A40">
+        <f>A35+($Q35*1000)</f>
+        <v>148000</v>
+      </c>
+      <c r="B40" t="s">
+        <v>19</v>
+      </c>
+      <c r="C40" t="s">
+        <v>41</v>
+      </c>
+      <c r="D40">
+        <f>D35+($Q35*1000)</f>
+        <v>148000</v>
+      </c>
+      <c r="E40" t="s">
+        <v>19</v>
+      </c>
+      <c r="F40" t="s">
+        <v>41</v>
+      </c>
+      <c r="G40">
+        <f t="shared" si="2"/>
+        <v>156000</v>
+      </c>
+      <c r="H40" t="s">
+        <v>19</v>
+      </c>
+      <c r="I40" t="s">
+        <v>42</v>
+      </c>
+      <c r="J40">
+        <f>J39+($S$2)</f>
+        <v>156000</v>
+      </c>
+      <c r="K40" t="s">
+        <v>31</v>
+      </c>
+      <c r="L40" t="s">
         <v>39</v>
       </c>
-      <c r="M39">
-        <f>M34+($Q34*1000)</f>
-        <v>168000</v>
-      </c>
-      <c r="N39" t="s">
-        <v>19</v>
-      </c>
-      <c r="O39" t="s">
+      <c r="M40">
+        <f>M35+($Q35*1000)</f>
+        <v>148000</v>
+      </c>
+      <c r="N40" t="s">
+        <v>19</v>
+      </c>
+      <c r="O40" t="s">
         <v>41</v>
       </c>
-      <c r="P39">
-        <v>8</v>
-      </c>
-      <c r="Q39">
+      <c r="P40">
+        <f>P35+1</f>
+        <v>9</v>
+      </c>
+      <c r="Q40">
         <v>10</v>
-      </c>
-    </row>
-    <row r="40" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="J40">
-        <f>J39+1000</f>
-        <v>177000</v>
-      </c>
-      <c r="K40" t="s">
-        <v>19</v>
-      </c>
-      <c r="L40" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="41" spans="1:18" x14ac:dyDescent="0.2">
       <c r="J41">
-        <f>J40+3000</f>
-        <v>180000</v>
+        <f>J40+1000</f>
+        <v>157000</v>
       </c>
       <c r="K41" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="L41" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="42" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="J42">
+        <f>J41+3000</f>
+        <v>160000</v>
+      </c>
+      <c r="K42" t="s">
+        <v>31</v>
+      </c>
+      <c r="L42" t="s">
         <v>39</v>
-      </c>
-    </row>
-    <row r="42" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A42">
-        <f>A39+($Q39*1000)</f>
-        <v>178000</v>
-      </c>
-      <c r="B42" t="s">
-        <v>19</v>
-      </c>
-      <c r="C42" t="s">
-        <v>44</v>
-      </c>
-      <c r="D42">
-        <f>D39+($Q39*1000)</f>
-        <v>178000</v>
-      </c>
-      <c r="E42" t="s">
-        <v>19</v>
-      </c>
-      <c r="F42" t="s">
-        <v>65</v>
-      </c>
-      <c r="G42">
-        <f>G39+Q39*1000</f>
-        <v>186000</v>
-      </c>
-      <c r="H42" t="s">
-        <v>31</v>
-      </c>
-      <c r="I42" t="s">
-        <v>43</v>
-      </c>
-      <c r="J42">
-        <f>J41+6000</f>
-        <v>186000</v>
-      </c>
-      <c r="K42" t="s">
-        <v>19</v>
-      </c>
-      <c r="L42" t="s">
-        <v>43</v>
-      </c>
-      <c r="M42">
-        <f>M39+($Q39*1000)</f>
-        <v>178000</v>
-      </c>
-      <c r="N42" t="s">
-        <v>19</v>
-      </c>
-      <c r="O42" t="s">
-        <v>65</v>
-      </c>
-      <c r="P42">
-        <v>9</v>
-      </c>
-      <c r="Q42">
-        <v>6</v>
-      </c>
-      <c r="R42" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="43" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A43">
-        <f t="shared" ref="A43:A48" si="3">A42+($Q42*1000)</f>
-        <v>184000</v>
+        <f>A40+($Q40*1000)</f>
+        <v>158000</v>
       </c>
       <c r="B43" t="s">
         <v>19</v>
       </c>
       <c r="C43" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D43">
-        <f t="shared" ref="D43:D48" si="4">D42+($Q42*1000)</f>
-        <v>184000</v>
+        <f>D40+($Q40*1000)</f>
+        <v>158000</v>
       </c>
       <c r="E43" t="s">
         <v>19</v>
       </c>
       <c r="F43" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="G43">
-        <f t="shared" ref="G43:G48" si="5">G42+$Q42*1000</f>
-        <v>192000</v>
+        <f>G40+Q40*1000</f>
+        <v>166000</v>
       </c>
       <c r="H43" t="s">
-        <v>60</v>
+        <v>31</v>
+      </c>
+      <c r="I43" t="s">
+        <v>43</v>
       </c>
       <c r="J43">
-        <f t="shared" ref="J43:J48" si="6">J42+$Q42*1000</f>
-        <v>192000</v>
+        <f>J42+6000</f>
+        <v>166000</v>
       </c>
       <c r="K43" t="s">
-        <v>60</v>
+        <v>19</v>
+      </c>
+      <c r="L43" t="s">
+        <v>43</v>
       </c>
       <c r="M43">
-        <f t="shared" ref="M43:M48" si="7">M42+($Q42*1000)</f>
-        <v>184000</v>
+        <f>M40+($Q40*1000)</f>
+        <v>158000</v>
       </c>
       <c r="N43" t="s">
         <v>19</v>
       </c>
       <c r="O43" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="P43">
+        <f>P40+1</f>
         <v>10</v>
       </c>
       <c r="Q43">
-        <v>35</v>
+        <v>6</v>
+      </c>
+      <c r="R43" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="44" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A44">
-        <f t="shared" si="3"/>
-        <v>219000</v>
+        <f t="shared" ref="A44:A49" si="3">A43+($Q43*1000)</f>
+        <v>164000</v>
       </c>
       <c r="B44" t="s">
         <v>19</v>
       </c>
       <c r="C44" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D44">
-        <f t="shared" si="4"/>
-        <v>219000</v>
+        <f t="shared" ref="D44:D49" si="4">D43+($Q43*1000)</f>
+        <v>164000</v>
       </c>
       <c r="E44" t="s">
         <v>19</v>
       </c>
       <c r="F44" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G44">
-        <f t="shared" si="5"/>
-        <v>227000</v>
+        <f t="shared" ref="G44:G49" si="5">G43+$Q43*1000</f>
+        <v>172000</v>
       </c>
       <c r="H44" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="J44">
-        <f t="shared" si="6"/>
-        <v>227000</v>
+        <f t="shared" ref="J44:J49" si="6">J43+$Q43*1000</f>
+        <v>172000</v>
       </c>
       <c r="K44" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="M44">
-        <f t="shared" si="7"/>
-        <v>219000</v>
+        <f t="shared" ref="M44:M49" si="7">M43+($Q43*1000)</f>
+        <v>164000</v>
       </c>
       <c r="N44" t="s">
         <v>19</v>
       </c>
       <c r="O44" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="P44">
+        <f>P43+1</f>
         <v>11</v>
       </c>
       <c r="Q44">
-        <v>21</v>
+        <v>35</v>
       </c>
     </row>
     <row r="45" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A45">
         <f t="shared" si="3"/>
-        <v>240000</v>
+        <v>199000</v>
       </c>
       <c r="B45" t="s">
         <v>19</v>
       </c>
       <c r="C45" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D45">
         <f t="shared" si="4"/>
-        <v>240000</v>
+        <v>199000</v>
       </c>
       <c r="E45" t="s">
         <v>19</v>
       </c>
       <c r="F45" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G45">
         <f t="shared" si="5"/>
-        <v>248000</v>
+        <v>207000</v>
       </c>
       <c r="H45" t="s">
         <v>62</v>
       </c>
       <c r="J45">
         <f t="shared" si="6"/>
-        <v>248000</v>
+        <v>207000</v>
       </c>
       <c r="K45" t="s">
-        <v>31</v>
-      </c>
-      <c r="L45" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="M45">
         <f t="shared" si="7"/>
-        <v>240000</v>
+        <v>199000</v>
       </c>
       <c r="N45" t="s">
         <v>19</v>
       </c>
       <c r="O45" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="P45">
+        <f t="shared" ref="P45:P49" si="8">P44+1</f>
         <v>12</v>
       </c>
       <c r="Q45">
-        <v>4</v>
+        <v>21</v>
       </c>
     </row>
     <row r="46" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A46">
         <f t="shared" si="3"/>
-        <v>244000</v>
+        <v>220000</v>
       </c>
       <c r="B46" t="s">
         <v>19</v>
@@ -2710,7 +2712,7 @@
       </c>
       <c r="D46">
         <f t="shared" si="4"/>
-        <v>244000</v>
+        <v>220000</v>
       </c>
       <c r="E46" t="s">
         <v>19</v>
@@ -2720,17 +2722,14 @@
       </c>
       <c r="G46">
         <f t="shared" si="5"/>
-        <v>252000</v>
+        <v>228000</v>
       </c>
       <c r="H46" t="s">
-        <v>31</v>
-      </c>
-      <c r="I46" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="J46">
         <f t="shared" si="6"/>
-        <v>252000</v>
+        <v>228000</v>
       </c>
       <c r="K46" t="s">
         <v>31</v>
@@ -2740,7 +2739,7 @@
       </c>
       <c r="M46">
         <f t="shared" si="7"/>
-        <v>244000</v>
+        <v>220000</v>
       </c>
       <c r="N46" t="s">
         <v>19</v>
@@ -2749,6 +2748,7 @@
         <v>48</v>
       </c>
       <c r="P46">
+        <f t="shared" si="8"/>
         <v>13</v>
       </c>
       <c r="Q46">
@@ -2758,1108 +2758,1176 @@
     <row r="47" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A47">
         <f t="shared" si="3"/>
-        <v>248000</v>
+        <v>224000</v>
       </c>
       <c r="B47" t="s">
         <v>19</v>
       </c>
       <c r="C47" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D47">
         <f t="shared" si="4"/>
-        <v>248000</v>
+        <v>224000</v>
       </c>
       <c r="E47" t="s">
         <v>19</v>
       </c>
       <c r="F47" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="G47">
         <f t="shared" si="5"/>
-        <v>256000</v>
+        <v>232000</v>
       </c>
       <c r="H47" t="s">
         <v>31</v>
       </c>
       <c r="I47" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="J47">
         <f t="shared" si="6"/>
-        <v>256000</v>
+        <v>232000</v>
       </c>
       <c r="K47" t="s">
         <v>31</v>
       </c>
       <c r="L47" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="M47">
         <f t="shared" si="7"/>
-        <v>248000</v>
+        <v>224000</v>
       </c>
       <c r="N47" t="s">
         <v>19</v>
       </c>
       <c r="O47" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="P47">
+        <f t="shared" si="8"/>
         <v>14</v>
       </c>
       <c r="Q47">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="48" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A48">
         <f t="shared" si="3"/>
-        <v>250000</v>
+        <v>228000</v>
       </c>
       <c r="B48" t="s">
         <v>19</v>
       </c>
       <c r="C48" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="D48">
         <f t="shared" si="4"/>
-        <v>250000</v>
+        <v>228000</v>
       </c>
       <c r="E48" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="F48" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="G48">
         <f t="shared" si="5"/>
-        <v>258000</v>
+        <v>236000</v>
       </c>
       <c r="H48" t="s">
         <v>31</v>
       </c>
       <c r="I48" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="J48">
         <f t="shared" si="6"/>
-        <v>258000</v>
+        <v>236000</v>
       </c>
       <c r="K48" t="s">
         <v>31</v>
       </c>
       <c r="L48" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="M48">
         <f t="shared" si="7"/>
-        <v>250000</v>
+        <v>228000</v>
       </c>
       <c r="N48" t="s">
         <v>19</v>
       </c>
       <c r="O48" t="s">
+        <v>50</v>
+      </c>
+      <c r="P48">
+        <f t="shared" si="8"/>
+        <v>15</v>
+      </c>
+      <c r="Q48">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A49">
+        <f t="shared" si="3"/>
+        <v>230000</v>
+      </c>
+      <c r="B49" t="s">
+        <v>19</v>
+      </c>
+      <c r="C49" t="s">
         <v>30</v>
       </c>
-      <c r="P48">
-        <v>15</v>
-      </c>
-      <c r="Q48">
+      <c r="D49">
+        <f t="shared" si="4"/>
+        <v>230000</v>
+      </c>
+      <c r="E49" t="s">
+        <v>31</v>
+      </c>
+      <c r="F49" t="s">
+        <v>52</v>
+      </c>
+      <c r="G49">
+        <f t="shared" si="5"/>
+        <v>238000</v>
+      </c>
+      <c r="H49" t="s">
+        <v>31</v>
+      </c>
+      <c r="I49" t="s">
+        <v>32</v>
+      </c>
+      <c r="J49">
+        <f t="shared" si="6"/>
+        <v>238000</v>
+      </c>
+      <c r="K49" t="s">
+        <v>31</v>
+      </c>
+      <c r="L49" t="s">
+        <v>33</v>
+      </c>
+      <c r="M49">
+        <f t="shared" si="7"/>
+        <v>230000</v>
+      </c>
+      <c r="N49" t="s">
+        <v>19</v>
+      </c>
+      <c r="O49" t="s">
+        <v>30</v>
+      </c>
+      <c r="P49">
+        <f t="shared" si="8"/>
+        <v>16</v>
+      </c>
+      <c r="Q49">
         <v>24</v>
-      </c>
-    </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="D49">
-        <f>D48+($S$2*(1-$R$2))</f>
-        <v>253950</v>
-      </c>
-      <c r="E49" t="s">
-        <v>19</v>
-      </c>
-      <c r="F49" t="s">
-        <v>53</v>
-      </c>
-      <c r="G49">
-        <f t="shared" ref="G49:G66" si="8">G48+($S$2)</f>
-        <v>262000</v>
-      </c>
-      <c r="H49" t="s">
-        <v>19</v>
-      </c>
-      <c r="I49" t="s">
-        <v>34</v>
-      </c>
-      <c r="J49">
-        <f>J48+($S$2*(1+$R$2))</f>
-        <v>262050</v>
-      </c>
-      <c r="K49" t="s">
-        <v>19</v>
-      </c>
-      <c r="L49" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="50" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D50">
         <f>D49+($S$2*(1-$R$2))</f>
-        <v>257900</v>
+        <v>233950</v>
       </c>
       <c r="E50" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="F50" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G50">
-        <f t="shared" si="8"/>
-        <v>266000</v>
+        <f t="shared" ref="G50:G67" si="9">G49+($S$2)</f>
+        <v>242000</v>
       </c>
       <c r="H50" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="I50" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J50">
-        <f t="shared" ref="J50:J69" si="9">J49+($S$2*(1+$R$2))</f>
-        <v>266100</v>
+        <f>J49+($S$2*(1+$R$2))</f>
+        <v>242050</v>
       </c>
       <c r="K50" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="L50" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="51" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D51">
-        <f t="shared" ref="D51:D72" si="10">D50+($S$2*(1-$R$2))</f>
-        <v>261850</v>
+        <f>D50+($S$2*(1-$R$2))</f>
+        <v>237900</v>
       </c>
       <c r="E51" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="F51" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G51">
-        <f t="shared" si="8"/>
-        <v>270000</v>
+        <f t="shared" si="9"/>
+        <v>246000</v>
       </c>
       <c r="H51" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="I51" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="J51">
-        <f t="shared" si="9"/>
-        <v>270150</v>
+        <f t="shared" ref="J51:J70" si="10">J50+($S$2*(1+$R$2))</f>
+        <v>246100</v>
       </c>
       <c r="K51" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="L51" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="52" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D52">
+        <f t="shared" ref="D52:D73" si="11">D51+($S$2*(1-$R$2))</f>
+        <v>241850</v>
+      </c>
+      <c r="E52" t="s">
+        <v>19</v>
+      </c>
+      <c r="F52" t="s">
+        <v>53</v>
+      </c>
+      <c r="G52">
+        <f t="shared" si="9"/>
+        <v>250000</v>
+      </c>
+      <c r="H52" t="s">
+        <v>19</v>
+      </c>
+      <c r="I52" t="s">
+        <v>34</v>
+      </c>
+      <c r="J52">
         <f t="shared" si="10"/>
-        <v>265800</v>
-      </c>
-      <c r="E52" t="s">
-        <v>31</v>
-      </c>
-      <c r="F52" t="s">
-        <v>52</v>
-      </c>
-      <c r="G52">
-        <f t="shared" si="8"/>
-        <v>274000</v>
-      </c>
-      <c r="H52" t="s">
-        <v>31</v>
-      </c>
-      <c r="I52" t="s">
-        <v>32</v>
-      </c>
-      <c r="J52">
-        <f t="shared" si="9"/>
-        <v>274200</v>
+        <v>250150</v>
       </c>
       <c r="K52" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="L52" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="53" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D53">
+        <f t="shared" si="11"/>
+        <v>245800</v>
+      </c>
+      <c r="E53" t="s">
+        <v>31</v>
+      </c>
+      <c r="F53" t="s">
+        <v>52</v>
+      </c>
+      <c r="G53">
+        <f t="shared" si="9"/>
+        <v>254000</v>
+      </c>
+      <c r="H53" t="s">
+        <v>31</v>
+      </c>
+      <c r="I53" t="s">
+        <v>32</v>
+      </c>
+      <c r="J53">
         <f t="shared" si="10"/>
-        <v>269750</v>
-      </c>
-      <c r="E53" t="s">
-        <v>19</v>
-      </c>
-      <c r="F53" t="s">
+        <v>254200</v>
+      </c>
+      <c r="K53" t="s">
+        <v>31</v>
+      </c>
+      <c r="L53" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="54" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="D54">
+        <f t="shared" si="11"/>
+        <v>249750</v>
+      </c>
+      <c r="E54" t="s">
+        <v>19</v>
+      </c>
+      <c r="F54" t="s">
         <v>53</v>
       </c>
-      <c r="G53">
-        <f t="shared" si="8"/>
-        <v>278000</v>
-      </c>
-      <c r="H53" t="s">
-        <v>19</v>
-      </c>
-      <c r="I53" t="s">
+      <c r="G54">
+        <f t="shared" si="9"/>
+        <v>258000</v>
+      </c>
+      <c r="H54" t="s">
+        <v>19</v>
+      </c>
+      <c r="I54" t="s">
         <v>34</v>
       </c>
-      <c r="J53">
+      <c r="J54">
+        <f t="shared" si="10"/>
+        <v>258250</v>
+      </c>
+      <c r="K54" t="s">
+        <v>19</v>
+      </c>
+      <c r="L54" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="55" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A55">
+        <f>A49+(Q49*1000)-((G54-D55)*0.5)</f>
+        <v>251850</v>
+      </c>
+      <c r="B55" t="s">
+        <v>31</v>
+      </c>
+      <c r="C55" t="s">
+        <v>39</v>
+      </c>
+      <c r="D55">
+        <f t="shared" si="11"/>
+        <v>253700</v>
+      </c>
+      <c r="E55" t="s">
+        <v>31</v>
+      </c>
+      <c r="F55" t="s">
+        <v>52</v>
+      </c>
+      <c r="G55">
         <f t="shared" si="9"/>
-        <v>278250</v>
-      </c>
-      <c r="K53" t="s">
-        <v>19</v>
-      </c>
-      <c r="L53" t="s">
+        <v>262000</v>
+      </c>
+      <c r="H55" t="s">
+        <v>31</v>
+      </c>
+      <c r="I55" t="s">
+        <v>32</v>
+      </c>
+      <c r="J55">
+        <f t="shared" si="10"/>
+        <v>262300</v>
+      </c>
+      <c r="K55" t="s">
+        <v>31</v>
+      </c>
+      <c r="L55" t="s">
+        <v>33</v>
+      </c>
+      <c r="M55">
+        <f>M49+($Q49*1000)</f>
+        <v>254000</v>
+      </c>
+      <c r="N55" t="s">
+        <v>19</v>
+      </c>
+      <c r="O55" t="s">
+        <v>36</v>
+      </c>
+      <c r="P55">
+        <f>P49+1</f>
+        <v>17</v>
+      </c>
+      <c r="Q55">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="56" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="D56">
+        <f t="shared" si="11"/>
+        <v>257650</v>
+      </c>
+      <c r="E56" t="s">
+        <v>19</v>
+      </c>
+      <c r="F56" t="s">
+        <v>53</v>
+      </c>
+      <c r="G56">
+        <f t="shared" si="9"/>
+        <v>266000</v>
+      </c>
+      <c r="H56" t="s">
+        <v>19</v>
+      </c>
+      <c r="I56" t="s">
+        <v>34</v>
+      </c>
+      <c r="J56">
+        <f t="shared" si="10"/>
+        <v>266350</v>
+      </c>
+      <c r="K56" t="s">
+        <v>19</v>
+      </c>
+      <c r="L56" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A54">
-        <f>A48+(Q48*1000)-((G53-D54)*0.5)</f>
-        <v>271850</v>
-      </c>
-      <c r="B54" t="s">
-        <v>31</v>
-      </c>
-      <c r="C54" t="s">
-        <v>39</v>
-      </c>
-      <c r="D54">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A57" t="s">
+        <v>66</v>
+      </c>
+      <c r="D57">
+        <f t="shared" si="11"/>
+        <v>261600</v>
+      </c>
+      <c r="E57" t="s">
+        <v>31</v>
+      </c>
+      <c r="F57" t="s">
+        <v>52</v>
+      </c>
+      <c r="G57">
+        <f t="shared" si="9"/>
+        <v>270000</v>
+      </c>
+      <c r="H57" t="s">
+        <v>31</v>
+      </c>
+      <c r="I57" t="s">
+        <v>32</v>
+      </c>
+      <c r="J57">
         <f t="shared" si="10"/>
-        <v>273700</v>
-      </c>
-      <c r="E54" t="s">
-        <v>31</v>
-      </c>
-      <c r="F54" t="s">
-        <v>52</v>
-      </c>
-      <c r="G54">
-        <f t="shared" si="8"/>
-        <v>282000</v>
-      </c>
-      <c r="H54" t="s">
-        <v>31</v>
-      </c>
-      <c r="I54" t="s">
-        <v>32</v>
-      </c>
-      <c r="J54">
-        <f t="shared" si="9"/>
-        <v>282300</v>
-      </c>
-      <c r="K54" t="s">
-        <v>31</v>
-      </c>
-      <c r="L54" t="s">
+        <v>270400</v>
+      </c>
+      <c r="K57" t="s">
+        <v>31</v>
+      </c>
+      <c r="L57" t="s">
         <v>33</v>
-      </c>
-      <c r="M54">
-        <f>M48+($Q48*1000)</f>
-        <v>274000</v>
-      </c>
-      <c r="N54" t="s">
-        <v>19</v>
-      </c>
-      <c r="O54" t="s">
-        <v>36</v>
-      </c>
-      <c r="P54">
-        <v>16</v>
-      </c>
-      <c r="Q54">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="D55">
-        <f t="shared" si="10"/>
-        <v>277650</v>
-      </c>
-      <c r="E55" t="s">
-        <v>19</v>
-      </c>
-      <c r="F55" t="s">
-        <v>53</v>
-      </c>
-      <c r="G55">
-        <f t="shared" si="8"/>
-        <v>286000</v>
-      </c>
-      <c r="H55" t="s">
-        <v>19</v>
-      </c>
-      <c r="I55" t="s">
-        <v>34</v>
-      </c>
-      <c r="J55">
-        <f t="shared" si="9"/>
-        <v>286350</v>
-      </c>
-      <c r="K55" t="s">
-        <v>19</v>
-      </c>
-      <c r="L55" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A56" t="s">
-        <v>66</v>
-      </c>
-      <c r="D56">
-        <f t="shared" si="10"/>
-        <v>281600</v>
-      </c>
-      <c r="E56" t="s">
-        <v>31</v>
-      </c>
-      <c r="F56" t="s">
-        <v>52</v>
-      </c>
-      <c r="G56">
-        <f t="shared" si="8"/>
-        <v>290000</v>
-      </c>
-      <c r="H56" t="s">
-        <v>31</v>
-      </c>
-      <c r="I56" t="s">
-        <v>32</v>
-      </c>
-      <c r="J56">
-        <f t="shared" si="9"/>
-        <v>290400</v>
-      </c>
-      <c r="K56" t="s">
-        <v>31</v>
-      </c>
-      <c r="L56" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A57">
-        <f>G48+($S$2*(1-$R$2*2))*10</f>
-        <v>297000</v>
-      </c>
-      <c r="B57" t="s">
-        <v>19</v>
-      </c>
-      <c r="C57" t="s">
-        <v>54</v>
-      </c>
-      <c r="D57">
-        <f t="shared" si="10"/>
-        <v>285550</v>
-      </c>
-      <c r="E57" t="s">
-        <v>19</v>
-      </c>
-      <c r="F57" t="s">
-        <v>53</v>
-      </c>
-      <c r="G57">
-        <f t="shared" si="8"/>
-        <v>294000</v>
-      </c>
-      <c r="H57" t="s">
-        <v>19</v>
-      </c>
-      <c r="I57" t="s">
-        <v>34</v>
-      </c>
-      <c r="J57">
-        <f t="shared" si="9"/>
-        <v>294450</v>
-      </c>
-      <c r="K57" t="s">
-        <v>19</v>
-      </c>
-      <c r="L57" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="58" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A58">
-        <f t="shared" ref="A58:A71" si="11">A57+($S$2*(1-$R$2*2))</f>
-        <v>300900</v>
+        <f>G49+($S$2*(1-$R$2*2))*10</f>
+        <v>277000</v>
       </c>
       <c r="B58" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="C58" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D58">
+        <f t="shared" si="11"/>
+        <v>265550</v>
+      </c>
+      <c r="E58" t="s">
+        <v>19</v>
+      </c>
+      <c r="F58" t="s">
+        <v>53</v>
+      </c>
+      <c r="G58">
+        <f t="shared" si="9"/>
+        <v>274000</v>
+      </c>
+      <c r="H58" t="s">
+        <v>19</v>
+      </c>
+      <c r="I58" t="s">
+        <v>34</v>
+      </c>
+      <c r="J58">
         <f t="shared" si="10"/>
-        <v>289500</v>
-      </c>
-      <c r="E58" t="s">
-        <v>31</v>
-      </c>
-      <c r="F58" t="s">
-        <v>52</v>
-      </c>
-      <c r="G58">
-        <f t="shared" si="8"/>
-        <v>298000</v>
-      </c>
-      <c r="H58" t="s">
-        <v>31</v>
-      </c>
-      <c r="I58" t="s">
-        <v>32</v>
-      </c>
-      <c r="J58">
-        <f t="shared" si="9"/>
-        <v>298500</v>
+        <v>274450</v>
       </c>
       <c r="K58" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="L58" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="59" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A59">
+        <f t="shared" ref="A59:A72" si="12">A58+($S$2*(1-$R$2*2))</f>
+        <v>280900</v>
+      </c>
+      <c r="B59" t="s">
+        <v>31</v>
+      </c>
+      <c r="C59" t="s">
+        <v>55</v>
+      </c>
+      <c r="D59">
         <f t="shared" si="11"/>
-        <v>304800</v>
-      </c>
-      <c r="B59" t="s">
-        <v>19</v>
-      </c>
-      <c r="C59" t="s">
-        <v>54</v>
-      </c>
-      <c r="D59">
+        <v>269500</v>
+      </c>
+      <c r="E59" t="s">
+        <v>31</v>
+      </c>
+      <c r="F59" t="s">
+        <v>52</v>
+      </c>
+      <c r="G59">
+        <f t="shared" si="9"/>
+        <v>278000</v>
+      </c>
+      <c r="H59" t="s">
+        <v>31</v>
+      </c>
+      <c r="I59" t="s">
+        <v>32</v>
+      </c>
+      <c r="J59">
         <f t="shared" si="10"/>
-        <v>293450</v>
-      </c>
-      <c r="E59" t="s">
-        <v>19</v>
-      </c>
-      <c r="F59" t="s">
-        <v>53</v>
-      </c>
-      <c r="G59">
-        <f t="shared" si="8"/>
-        <v>302000</v>
-      </c>
-      <c r="H59" t="s">
-        <v>19</v>
-      </c>
-      <c r="I59" t="s">
-        <v>34</v>
-      </c>
-      <c r="J59">
-        <f t="shared" si="9"/>
-        <v>302550</v>
+        <v>278500</v>
       </c>
       <c r="K59" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="L59" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="60" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A60">
+        <f t="shared" si="12"/>
+        <v>284800</v>
+      </c>
+      <c r="B60" t="s">
+        <v>19</v>
+      </c>
+      <c r="C60" t="s">
+        <v>54</v>
+      </c>
+      <c r="D60">
         <f t="shared" si="11"/>
-        <v>308700</v>
-      </c>
-      <c r="B60" t="s">
-        <v>31</v>
-      </c>
-      <c r="C60" t="s">
-        <v>55</v>
-      </c>
-      <c r="D60">
+        <v>273450</v>
+      </c>
+      <c r="E60" t="s">
+        <v>19</v>
+      </c>
+      <c r="F60" t="s">
+        <v>53</v>
+      </c>
+      <c r="G60">
+        <f t="shared" si="9"/>
+        <v>282000</v>
+      </c>
+      <c r="H60" t="s">
+        <v>19</v>
+      </c>
+      <c r="I60" t="s">
+        <v>34</v>
+      </c>
+      <c r="J60">
         <f t="shared" si="10"/>
-        <v>297400</v>
-      </c>
-      <c r="E60" t="s">
-        <v>31</v>
-      </c>
-      <c r="F60" t="s">
-        <v>52</v>
-      </c>
-      <c r="G60">
-        <f t="shared" si="8"/>
-        <v>306000</v>
-      </c>
-      <c r="H60" t="s">
-        <v>31</v>
-      </c>
-      <c r="I60" t="s">
-        <v>32</v>
-      </c>
-      <c r="J60">
-        <f t="shared" si="9"/>
-        <v>306600</v>
+        <v>282550</v>
       </c>
       <c r="K60" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="L60" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="61" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A61">
+        <f t="shared" si="12"/>
+        <v>288700</v>
+      </c>
+      <c r="B61" t="s">
+        <v>31</v>
+      </c>
+      <c r="C61" t="s">
+        <v>55</v>
+      </c>
+      <c r="D61">
         <f t="shared" si="11"/>
-        <v>312600</v>
-      </c>
-      <c r="B61" t="s">
-        <v>19</v>
-      </c>
-      <c r="C61" t="s">
-        <v>54</v>
-      </c>
-      <c r="D61">
+        <v>277400</v>
+      </c>
+      <c r="E61" t="s">
+        <v>31</v>
+      </c>
+      <c r="F61" t="s">
+        <v>52</v>
+      </c>
+      <c r="G61">
+        <f t="shared" si="9"/>
+        <v>286000</v>
+      </c>
+      <c r="H61" t="s">
+        <v>31</v>
+      </c>
+      <c r="I61" t="s">
+        <v>32</v>
+      </c>
+      <c r="J61">
         <f t="shared" si="10"/>
-        <v>301350</v>
-      </c>
-      <c r="E61" t="s">
-        <v>19</v>
-      </c>
-      <c r="F61" t="s">
-        <v>53</v>
-      </c>
-      <c r="G61">
-        <f t="shared" si="8"/>
-        <v>310000</v>
-      </c>
-      <c r="H61" t="s">
-        <v>19</v>
-      </c>
-      <c r="I61" t="s">
-        <v>34</v>
-      </c>
-      <c r="J61">
-        <f t="shared" si="9"/>
-        <v>310650</v>
+        <v>286600</v>
       </c>
       <c r="K61" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="L61" t="s">
-        <v>35</v>
-      </c>
-      <c r="M61">
-        <f>M54+($Q54*1000)</f>
-        <v>302000</v>
-      </c>
-      <c r="N61" t="s">
-        <v>19</v>
-      </c>
-      <c r="O61" t="s">
-        <v>56</v>
-      </c>
-      <c r="P61">
-        <v>17</v>
-      </c>
-      <c r="Q61">
-        <v>20</v>
+        <v>33</v>
       </c>
     </row>
     <row r="62" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A62">
+        <f t="shared" si="12"/>
+        <v>292600</v>
+      </c>
+      <c r="B62" t="s">
+        <v>19</v>
+      </c>
+      <c r="C62" t="s">
+        <v>54</v>
+      </c>
+      <c r="D62">
         <f t="shared" si="11"/>
-        <v>316500</v>
-      </c>
-      <c r="B62" t="s">
-        <v>31</v>
-      </c>
-      <c r="C62" t="s">
-        <v>55</v>
-      </c>
-      <c r="D62">
+        <v>281350</v>
+      </c>
+      <c r="E62" t="s">
+        <v>19</v>
+      </c>
+      <c r="F62" t="s">
+        <v>53</v>
+      </c>
+      <c r="G62">
+        <f t="shared" si="9"/>
+        <v>290000</v>
+      </c>
+      <c r="H62" t="s">
+        <v>19</v>
+      </c>
+      <c r="I62" t="s">
+        <v>34</v>
+      </c>
+      <c r="J62">
         <f t="shared" si="10"/>
-        <v>305300</v>
-      </c>
-      <c r="E62" t="s">
-        <v>31</v>
-      </c>
-      <c r="F62" t="s">
-        <v>52</v>
-      </c>
-      <c r="G62">
-        <f t="shared" si="8"/>
-        <v>314000</v>
-      </c>
-      <c r="H62" t="s">
-        <v>31</v>
-      </c>
-      <c r="I62" t="s">
-        <v>32</v>
-      </c>
-      <c r="J62">
-        <f t="shared" si="9"/>
-        <v>314700</v>
+        <v>290650</v>
       </c>
       <c r="K62" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="L62" t="s">
-        <v>33</v>
+        <v>35</v>
+      </c>
+      <c r="M62">
+        <f>M55+($Q55*1000)</f>
+        <v>282000</v>
+      </c>
+      <c r="N62" t="s">
+        <v>19</v>
+      </c>
+      <c r="O62" t="s">
+        <v>56</v>
+      </c>
+      <c r="P62">
+        <f>P55+1</f>
+        <v>18</v>
+      </c>
+      <c r="Q62">
+        <v>20</v>
       </c>
     </row>
     <row r="63" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A63">
+        <f t="shared" si="12"/>
+        <v>296500</v>
+      </c>
+      <c r="B63" t="s">
+        <v>31</v>
+      </c>
+      <c r="C63" t="s">
+        <v>55</v>
+      </c>
+      <c r="D63">
         <f t="shared" si="11"/>
-        <v>320400</v>
-      </c>
-      <c r="B63" t="s">
-        <v>19</v>
-      </c>
-      <c r="C63" t="s">
-        <v>54</v>
-      </c>
-      <c r="D63">
+        <v>285300</v>
+      </c>
+      <c r="E63" t="s">
+        <v>31</v>
+      </c>
+      <c r="F63" t="s">
+        <v>52</v>
+      </c>
+      <c r="G63">
+        <f t="shared" si="9"/>
+        <v>294000</v>
+      </c>
+      <c r="H63" t="s">
+        <v>31</v>
+      </c>
+      <c r="I63" t="s">
+        <v>32</v>
+      </c>
+      <c r="J63">
         <f t="shared" si="10"/>
-        <v>309250</v>
-      </c>
-      <c r="E63" t="s">
-        <v>19</v>
-      </c>
-      <c r="F63" t="s">
-        <v>53</v>
-      </c>
-      <c r="G63">
-        <f t="shared" si="8"/>
-        <v>318000</v>
-      </c>
-      <c r="H63" t="s">
-        <v>19</v>
-      </c>
-      <c r="I63" t="s">
-        <v>34</v>
-      </c>
-      <c r="J63">
-        <f t="shared" si="9"/>
-        <v>318750</v>
+        <v>294700</v>
       </c>
       <c r="K63" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="L63" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="64" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A64">
+        <f t="shared" si="12"/>
+        <v>300400</v>
+      </c>
+      <c r="B64" t="s">
+        <v>19</v>
+      </c>
+      <c r="C64" t="s">
+        <v>54</v>
+      </c>
+      <c r="D64">
         <f t="shared" si="11"/>
-        <v>324300</v>
-      </c>
-      <c r="B64" t="s">
-        <v>31</v>
-      </c>
-      <c r="C64" t="s">
-        <v>55</v>
-      </c>
-      <c r="D64">
+        <v>289250</v>
+      </c>
+      <c r="E64" t="s">
+        <v>19</v>
+      </c>
+      <c r="F64" t="s">
+        <v>53</v>
+      </c>
+      <c r="G64">
+        <f t="shared" si="9"/>
+        <v>298000</v>
+      </c>
+      <c r="H64" t="s">
+        <v>19</v>
+      </c>
+      <c r="I64" t="s">
+        <v>34</v>
+      </c>
+      <c r="J64">
         <f t="shared" si="10"/>
-        <v>313200</v>
-      </c>
-      <c r="E64" t="s">
-        <v>31</v>
-      </c>
-      <c r="F64" t="s">
-        <v>52</v>
-      </c>
-      <c r="G64">
-        <f t="shared" si="8"/>
-        <v>322000</v>
-      </c>
-      <c r="H64" t="s">
-        <v>31</v>
-      </c>
-      <c r="I64" t="s">
-        <v>57</v>
-      </c>
-      <c r="J64">
-        <f t="shared" si="9"/>
-        <v>322800</v>
+        <v>298750</v>
       </c>
       <c r="K64" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="L64" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="65" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A65">
+        <f t="shared" si="12"/>
+        <v>304300</v>
+      </c>
+      <c r="B65" t="s">
+        <v>31</v>
+      </c>
+      <c r="C65" t="s">
+        <v>55</v>
+      </c>
+      <c r="D65">
         <f t="shared" si="11"/>
-        <v>328200</v>
-      </c>
-      <c r="B65" t="s">
-        <v>19</v>
-      </c>
-      <c r="C65" t="s">
-        <v>54</v>
-      </c>
-      <c r="D65">
+        <v>293200</v>
+      </c>
+      <c r="E65" t="s">
+        <v>31</v>
+      </c>
+      <c r="F65" t="s">
+        <v>52</v>
+      </c>
+      <c r="G65">
+        <f t="shared" si="9"/>
+        <v>302000</v>
+      </c>
+      <c r="H65" t="s">
+        <v>31</v>
+      </c>
+      <c r="I65" t="s">
+        <v>57</v>
+      </c>
+      <c r="J65">
         <f t="shared" si="10"/>
-        <v>317150</v>
-      </c>
-      <c r="E65" t="s">
-        <v>19</v>
-      </c>
-      <c r="F65" t="s">
-        <v>53</v>
-      </c>
-      <c r="G65">
-        <f t="shared" si="8"/>
-        <v>326000</v>
-      </c>
-      <c r="H65" t="s">
-        <v>19</v>
-      </c>
-      <c r="I65" t="s">
-        <v>43</v>
-      </c>
-      <c r="J65">
-        <f t="shared" si="9"/>
-        <v>326850</v>
+        <v>302800</v>
       </c>
       <c r="K65" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="L65" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="66" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A66">
+        <f t="shared" si="12"/>
+        <v>308200</v>
+      </c>
+      <c r="B66" t="s">
+        <v>19</v>
+      </c>
+      <c r="C66" t="s">
+        <v>54</v>
+      </c>
+      <c r="D66">
         <f t="shared" si="11"/>
-        <v>332100</v>
-      </c>
-      <c r="B66" t="s">
-        <v>31</v>
-      </c>
-      <c r="C66" t="s">
-        <v>55</v>
-      </c>
-      <c r="D66">
+        <v>297150</v>
+      </c>
+      <c r="E66" t="s">
+        <v>19</v>
+      </c>
+      <c r="F66" t="s">
+        <v>53</v>
+      </c>
+      <c r="G66">
+        <f t="shared" si="9"/>
+        <v>306000</v>
+      </c>
+      <c r="H66" t="s">
+        <v>19</v>
+      </c>
+      <c r="I66" t="s">
+        <v>43</v>
+      </c>
+      <c r="J66">
         <f t="shared" si="10"/>
-        <v>321100</v>
-      </c>
-      <c r="E66" t="s">
-        <v>31</v>
-      </c>
-      <c r="F66" t="s">
-        <v>52</v>
-      </c>
-      <c r="G66">
-        <f t="shared" si="8"/>
-        <v>330000</v>
-      </c>
-      <c r="H66" t="s">
-        <v>60</v>
-      </c>
-      <c r="J66">
-        <f t="shared" si="9"/>
-        <v>330900</v>
+        <v>306850</v>
       </c>
       <c r="K66" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="L66" t="s">
-        <v>33</v>
-      </c>
-      <c r="M66">
-        <f>M61+($Q61*1000)</f>
-        <v>322000</v>
-      </c>
-      <c r="N66" t="s">
-        <v>19</v>
-      </c>
-      <c r="O66" t="s">
-        <v>41</v>
-      </c>
-      <c r="P66">
-        <v>18</v>
-      </c>
-      <c r="Q66">
-        <v>10</v>
+        <v>35</v>
       </c>
     </row>
     <row r="67" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A67">
+        <f t="shared" si="12"/>
+        <v>312100</v>
+      </c>
+      <c r="B67" t="s">
+        <v>31</v>
+      </c>
+      <c r="C67" t="s">
+        <v>55</v>
+      </c>
+      <c r="D67">
         <f t="shared" si="11"/>
-        <v>336000</v>
-      </c>
-      <c r="B67" t="s">
-        <v>19</v>
-      </c>
-      <c r="C67" t="s">
-        <v>54</v>
-      </c>
-      <c r="D67">
+        <v>301100</v>
+      </c>
+      <c r="E67" t="s">
+        <v>31</v>
+      </c>
+      <c r="F67" t="s">
+        <v>52</v>
+      </c>
+      <c r="G67">
+        <f t="shared" si="9"/>
+        <v>310000</v>
+      </c>
+      <c r="H67" t="s">
+        <v>60</v>
+      </c>
+      <c r="J67">
         <f t="shared" si="10"/>
-        <v>325050</v>
-      </c>
-      <c r="E67" t="s">
-        <v>19</v>
-      </c>
-      <c r="F67" t="s">
-        <v>53</v>
-      </c>
-      <c r="J67">
-        <f t="shared" si="9"/>
-        <v>334950</v>
+        <v>310900</v>
       </c>
       <c r="K67" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="L67" t="s">
-        <v>35</v>
+        <v>33</v>
+      </c>
+      <c r="M67">
+        <f>M62+($Q62*1000)</f>
+        <v>302000</v>
+      </c>
+      <c r="N67" t="s">
+        <v>19</v>
+      </c>
+      <c r="O67" t="s">
+        <v>41</v>
+      </c>
+      <c r="P67">
+        <f>P62+1</f>
+        <v>19</v>
+      </c>
+      <c r="Q67">
+        <v>10</v>
       </c>
     </row>
     <row r="68" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A68">
+        <f t="shared" si="12"/>
+        <v>316000</v>
+      </c>
+      <c r="B68" t="s">
+        <v>19</v>
+      </c>
+      <c r="C68" t="s">
+        <v>54</v>
+      </c>
+      <c r="D68">
         <f t="shared" si="11"/>
-        <v>339900</v>
-      </c>
-      <c r="B68" t="s">
-        <v>31</v>
-      </c>
-      <c r="C68" t="s">
-        <v>55</v>
-      </c>
-      <c r="D68">
+        <v>305050</v>
+      </c>
+      <c r="E68" t="s">
+        <v>19</v>
+      </c>
+      <c r="F68" t="s">
+        <v>53</v>
+      </c>
+      <c r="J68">
         <f t="shared" si="10"/>
-        <v>329000</v>
-      </c>
-      <c r="E68" t="s">
-        <v>31</v>
-      </c>
-      <c r="F68" t="s">
-        <v>52</v>
-      </c>
-      <c r="G68">
-        <f>G66+$Q66*1000</f>
-        <v>340000</v>
-      </c>
-      <c r="H68" t="s">
-        <v>60</v>
-      </c>
-      <c r="J68">
-        <f t="shared" si="9"/>
-        <v>339000</v>
+        <v>314950</v>
       </c>
       <c r="K68" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="L68" t="s">
-        <v>33</v>
-      </c>
-      <c r="M68">
-        <f>M66+($Q66*1000)</f>
-        <v>332000</v>
-      </c>
-      <c r="N68" t="s">
-        <v>19</v>
-      </c>
-      <c r="O68" t="s">
-        <v>58</v>
-      </c>
-      <c r="P68">
-        <v>19</v>
-      </c>
-      <c r="Q68">
-        <v>15</v>
+        <v>35</v>
       </c>
     </row>
     <row r="69" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A69">
+        <f t="shared" si="12"/>
+        <v>319900</v>
+      </c>
+      <c r="B69" t="s">
+        <v>31</v>
+      </c>
+      <c r="C69" t="s">
+        <v>55</v>
+      </c>
+      <c r="D69">
         <f t="shared" si="11"/>
-        <v>343800</v>
-      </c>
-      <c r="B69" t="s">
-        <v>19</v>
-      </c>
-      <c r="C69" t="s">
-        <v>54</v>
-      </c>
-      <c r="D69">
+        <v>309000</v>
+      </c>
+      <c r="E69" t="s">
+        <v>31</v>
+      </c>
+      <c r="F69" t="s">
+        <v>52</v>
+      </c>
+      <c r="G69">
+        <f>G67+$Q67*1000</f>
+        <v>320000</v>
+      </c>
+      <c r="H69" t="s">
+        <v>60</v>
+      </c>
+      <c r="J69">
         <f t="shared" si="10"/>
-        <v>332950</v>
-      </c>
-      <c r="E69" t="s">
-        <v>19</v>
-      </c>
-      <c r="F69" t="s">
-        <v>53</v>
-      </c>
-      <c r="J69">
-        <f t="shared" si="9"/>
-        <v>343050</v>
+        <v>319000</v>
       </c>
       <c r="K69" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="L69" t="s">
-        <v>43</v>
+        <v>33</v>
+      </c>
+      <c r="M69">
+        <f>M67+($Q67*1000)</f>
+        <v>312000</v>
+      </c>
+      <c r="N69" t="s">
+        <v>19</v>
+      </c>
+      <c r="O69" t="s">
+        <v>58</v>
+      </c>
+      <c r="P69">
+        <f>P67+1</f>
+        <v>20</v>
+      </c>
+      <c r="Q69">
+        <v>15</v>
       </c>
     </row>
     <row r="70" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A70">
+        <f t="shared" si="12"/>
+        <v>323800</v>
+      </c>
+      <c r="B70" t="s">
+        <v>19</v>
+      </c>
+      <c r="C70" t="s">
+        <v>54</v>
+      </c>
+      <c r="D70">
         <f t="shared" si="11"/>
-        <v>347700</v>
-      </c>
-      <c r="B70" t="s">
-        <v>31</v>
-      </c>
-      <c r="C70" t="s">
-        <v>59</v>
-      </c>
-      <c r="D70">
+        <v>312950</v>
+      </c>
+      <c r="E70" t="s">
+        <v>19</v>
+      </c>
+      <c r="F70" t="s">
+        <v>53</v>
+      </c>
+      <c r="J70">
         <f t="shared" si="10"/>
-        <v>336900</v>
-      </c>
-      <c r="E70" t="s">
-        <v>31</v>
-      </c>
-      <c r="F70" t="s">
-        <v>52</v>
-      </c>
-      <c r="J70">
-        <f>J69+($S$2*(1+$R$2))</f>
-        <v>347100</v>
+        <v>323050</v>
       </c>
       <c r="K70" t="s">
-        <v>60</v>
+        <v>19</v>
+      </c>
+      <c r="L70" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="71" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A71">
+        <f t="shared" si="12"/>
+        <v>327700</v>
+      </c>
+      <c r="B71" t="s">
+        <v>31</v>
+      </c>
+      <c r="C71" t="s">
+        <v>59</v>
+      </c>
+      <c r="D71">
         <f t="shared" si="11"/>
-        <v>351600</v>
-      </c>
-      <c r="B71" t="s">
+        <v>316900</v>
+      </c>
+      <c r="E71" t="s">
+        <v>31</v>
+      </c>
+      <c r="F71" t="s">
+        <v>52</v>
+      </c>
+      <c r="J71">
+        <f>J70+($S$2*(1+$R$2))</f>
+        <v>327100</v>
+      </c>
+      <c r="K71" t="s">
         <v>60</v>
       </c>
-      <c r="D71">
-        <f t="shared" si="10"/>
-        <v>340850</v>
-      </c>
-      <c r="E71" t="s">
-        <v>19</v>
-      </c>
-      <c r="F71" t="s">
+    </row>
+    <row r="72" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A72">
+        <f t="shared" si="12"/>
+        <v>331600</v>
+      </c>
+      <c r="B72" t="s">
+        <v>60</v>
+      </c>
+      <c r="D72">
+        <f t="shared" si="11"/>
+        <v>320850</v>
+      </c>
+      <c r="E72" t="s">
+        <v>19</v>
+      </c>
+      <c r="F72" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="D72">
-        <f t="shared" si="10"/>
-        <v>344800</v>
-      </c>
-      <c r="E72" t="s">
+    <row r="73" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="D73">
+        <f t="shared" si="11"/>
+        <v>324800</v>
+      </c>
+      <c r="E73" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="G73">
-        <f>G68+$Q68*1000</f>
-        <v>355000</v>
-      </c>
-      <c r="H73" t="s">
+    <row r="74" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="G74">
+        <f>G69+$Q69*1000</f>
+        <v>335000</v>
+      </c>
+      <c r="H74" t="s">
         <v>62</v>
       </c>
-      <c r="M73">
-        <f>M68+($Q68*1000)</f>
-        <v>347000</v>
-      </c>
-      <c r="N73" t="s">
-        <v>19</v>
-      </c>
-      <c r="O73" t="s">
+      <c r="M74">
+        <f>M69+($Q69*1000)</f>
+        <v>327000</v>
+      </c>
+      <c r="N74" t="s">
+        <v>19</v>
+      </c>
+      <c r="O74" t="s">
         <v>61</v>
       </c>
-      <c r="P73">
-        <v>20</v>
-      </c>
-      <c r="Q73">
+      <c r="P74">
+        <f>P69+1</f>
+        <v>21</v>
+      </c>
+      <c r="Q74">
         <v>40</v>
       </c>
     </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="J82">
-        <f>J70+Q73*1000</f>
-        <v>387100</v>
-      </c>
-      <c r="K82" t="s">
+    <row r="83" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="J83">
+        <f>J71+Q74*1000</f>
+        <v>367100</v>
+      </c>
+      <c r="K83" t="s">
         <v>62</v>
       </c>
-      <c r="M82">
-        <f>M73+($Q73*1000)</f>
-        <v>387000</v>
-      </c>
-      <c r="N82" t="s">
-        <v>19</v>
-      </c>
-      <c r="O82" t="s">
+      <c r="M83">
+        <f>M74+($Q74*1000)</f>
+        <v>367000</v>
+      </c>
+      <c r="N83" t="s">
+        <v>19</v>
+      </c>
+      <c r="O83" t="s">
         <v>43</v>
       </c>
-      <c r="P82">
-        <v>21</v>
-      </c>
-      <c r="Q82">
+      <c r="P83">
+        <f>P74+1</f>
+        <v>22</v>
+      </c>
+      <c r="Q83">
         <v>5</v>
       </c>
     </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="D83">
+    <row r="84" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="D84">
         <v>318500</v>
       </c>
-      <c r="E83" t="s">
+      <c r="E84" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A84">
+    <row r="85" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A85">
         <v>321000</v>
       </c>
-      <c r="B84" t="s">
+      <c r="B85" t="s">
         <v>62</v>
       </c>
-      <c r="M84">
-        <f>M82+($Q82*1000)</f>
-        <v>392000</v>
-      </c>
-      <c r="N84" t="s">
-        <v>19</v>
-      </c>
-      <c r="O84" t="s">
+      <c r="M85">
+        <f>M83+($Q83*1000)</f>
+        <v>372000</v>
+      </c>
+      <c r="N85" t="s">
+        <v>19</v>
+      </c>
+      <c r="O85" t="s">
         <v>63</v>
       </c>
-      <c r="P84">
-        <v>22</v>
-      </c>
-      <c r="Q84">
+      <c r="P85">
+        <f>P83+1</f>
+        <v>23</v>
+      </c>
+      <c r="Q85">
         <v>100</v>
       </c>
     </row>

--- a/onsets_edit.xlsx
+++ b/onsets_edit.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/brandonwoosnyder/Dropbox/docs-d/00_UCI_2025-2026/02_UCI_Winter_2026/Independent Study Rajna - Music 299/Constrained_PhoneGuide_Score/ScreenTimeScore/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CADD9A4-F67A-8A4F-8662-F187C0B00684}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2705C24-35D6-6A40-B3B2-BBAE27ED7F71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="180" yWindow="840" windowWidth="30060" windowHeight="17180" xr2:uid="{656903FE-55D6-334E-8317-D02588440573}"/>
+    <workbookView xWindow="1080" yWindow="-18300" windowWidth="30060" windowHeight="15020" xr2:uid="{656903FE-55D6-334E-8317-D02588440573}"/>
   </bookViews>
   <sheets>
     <sheet name="onsets" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="511" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="549" uniqueCount="71">
   <si>
     <t>onset_ms_1</t>
   </si>
@@ -224,19 +224,28 @@
     <t>bacon01flash</t>
   </si>
   <si>
-    <t>PLAY</t>
-  </si>
-  <si>
     <t>bacon01rise</t>
   </si>
   <si>
     <t>Tacet 6"</t>
   </si>
   <si>
-    <t>IS THIS VALUE BELOW CORRECT???</t>
-  </si>
-  <si>
-    <t>bacon01bright</t>
+    <t>open final measure</t>
+  </si>
+  <si>
+    <t>flickering measure</t>
+  </si>
+  <si>
+    <t>OPEN FLASH</t>
+  </si>
+  <si>
+    <t>OPEN FADE AND REST</t>
+  </si>
+  <si>
+    <t>bacon01flickerheavy</t>
+  </si>
+  <si>
+    <t>bacon01flickersubtle</t>
   </si>
 </sst>
 </file>
@@ -1097,7 +1106,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E707C8EF-5282-2B42-BB2D-C2C257FF5AA3}">
-  <dimension ref="A1:S85"/>
+  <dimension ref="A1:S88"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="26.6640625" bestFit="1" customWidth="1"/>
@@ -1653,31 +1662,31 @@
         <v>10000</v>
       </c>
       <c r="B12" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D12">
         <v>10000</v>
       </c>
       <c r="E12" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G12">
         <v>10000</v>
       </c>
       <c r="H12" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J12">
         <v>10000</v>
       </c>
       <c r="K12" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="M12">
         <v>10000</v>
       </c>
       <c r="N12" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="P12">
         <f>P2+1</f>
@@ -1693,35 +1702,35 @@
         <v>30000</v>
       </c>
       <c r="B13" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D13">
         <f>D12+($Q12*1000)</f>
         <v>30000</v>
       </c>
       <c r="E13" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G13">
         <f>G12+($Q12*1000)</f>
         <v>30000</v>
       </c>
       <c r="H13" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="J13">
         <f>J12+($Q12*1000)</f>
         <v>30000</v>
       </c>
       <c r="K13" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="M13">
         <f>M12+($Q12*1000)</f>
         <v>30000</v>
       </c>
       <c r="N13" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="P13">
         <f>P12+1</f>
@@ -1740,7 +1749,7 @@
         <v>19</v>
       </c>
       <c r="C14" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D14">
         <f>D13+($Q13*1000)</f>
@@ -1750,7 +1759,7 @@
         <v>19</v>
       </c>
       <c r="F14" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G14">
         <f>G13+($Q13*1000)</f>
@@ -1760,7 +1769,7 @@
         <v>19</v>
       </c>
       <c r="I14" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J14">
         <f>J13+($Q13*1000)</f>
@@ -1770,7 +1779,7 @@
         <v>19</v>
       </c>
       <c r="L14" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="M14">
         <f>M13+($Q13*1000)</f>
@@ -1780,7 +1789,7 @@
         <v>19</v>
       </c>
       <c r="O14" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="P14">
         <f>P13+1</f>
@@ -2550,7 +2559,7 @@
         <v>19</v>
       </c>
       <c r="F43" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G43">
         <f>G40+Q40*1000</f>
@@ -2580,7 +2589,7 @@
         <v>19</v>
       </c>
       <c r="O43" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="P43">
         <f>P40+1</f>
@@ -2944,7 +2953,7 @@
         <v>53</v>
       </c>
       <c r="G50">
-        <f t="shared" ref="G50:G67" si="9">G49+($S$2)</f>
+        <f t="shared" ref="G50:G66" si="9">G49+($S$2)</f>
         <v>242000</v>
       </c>
       <c r="H50" t="s">
@@ -3184,9 +3193,6 @@
       </c>
     </row>
     <row r="57" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A57" t="s">
-        <v>66</v>
-      </c>
       <c r="D57">
         <f t="shared" si="11"/>
         <v>261600</v>
@@ -3635,7 +3641,7 @@
         <v>52</v>
       </c>
       <c r="G67">
-        <f t="shared" si="9"/>
+        <f>G66+($S$2)</f>
         <v>310000</v>
       </c>
       <c r="H67" t="s">
@@ -3847,12 +3853,33 @@
       </c>
     </row>
     <row r="74" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A74">
+        <f>$M74</f>
+        <v>327000</v>
+      </c>
+      <c r="B74" t="s">
+        <v>60</v>
+      </c>
+      <c r="D74">
+        <f>$M74</f>
+        <v>327000</v>
+      </c>
+      <c r="E74" t="s">
+        <v>60</v>
+      </c>
       <c r="G74">
-        <f>G69+$Q69*1000</f>
-        <v>335000</v>
+        <f>$M74</f>
+        <v>327000</v>
       </c>
       <c r="H74" t="s">
         <v>62</v>
+      </c>
+      <c r="J74">
+        <f>$M74</f>
+        <v>327000</v>
+      </c>
+      <c r="K74" t="s">
+        <v>60</v>
       </c>
       <c r="M74">
         <f>M69+($Q69*1000)</f>
@@ -3873,9 +3900,30 @@
       </c>
     </row>
     <row r="83" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A83">
+        <f>$M83</f>
+        <v>367000</v>
+      </c>
+      <c r="B83" t="s">
+        <v>60</v>
+      </c>
+      <c r="D83">
+        <f>$M83</f>
+        <v>367000</v>
+      </c>
+      <c r="E83" t="s">
+        <v>60</v>
+      </c>
+      <c r="G83">
+        <f>$M83</f>
+        <v>367000</v>
+      </c>
+      <c r="H83" t="s">
+        <v>62</v>
+      </c>
       <c r="J83">
-        <f>J71+Q74*1000</f>
-        <v>367100</v>
+        <f>$M83</f>
+        <v>367000</v>
       </c>
       <c r="K83" t="s">
         <v>62</v>
@@ -3900,7 +3948,8 @@
     </row>
     <row r="84" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D84">
-        <v>318500</v>
+        <f>((D85-D83)/2)+D83</f>
+        <v>369500</v>
       </c>
       <c r="E84" t="s">
         <v>62</v>
@@ -3908,9 +3957,31 @@
     </row>
     <row r="85" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A85">
-        <v>321000</v>
+        <f>$M85</f>
+        <v>372000</v>
       </c>
       <c r="B85" t="s">
+        <v>62</v>
+      </c>
+      <c r="D85">
+        <f>$M85</f>
+        <v>372000</v>
+      </c>
+      <c r="E85" t="s">
+        <v>62</v>
+      </c>
+      <c r="G85">
+        <f>$M85</f>
+        <v>372000</v>
+      </c>
+      <c r="H85" t="s">
+        <v>62</v>
+      </c>
+      <c r="J85">
+        <f>$M85</f>
+        <v>372000</v>
+      </c>
+      <c r="K85" t="s">
         <v>62</v>
       </c>
       <c r="M85">
@@ -3921,14 +3992,191 @@
         <v>19</v>
       </c>
       <c r="O85" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="P85">
         <f>P83+1</f>
         <v>23</v>
       </c>
       <c r="Q85">
-        <v>100</v>
+        <v>210</v>
+      </c>
+    </row>
+    <row r="86" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A86">
+        <f>A85+($Q85*1000)</f>
+        <v>582000</v>
+      </c>
+      <c r="B86" t="s">
+        <v>19</v>
+      </c>
+      <c r="C86" t="s">
+        <v>68</v>
+      </c>
+      <c r="D86">
+        <f>D85+($Q85*1000)</f>
+        <v>582000</v>
+      </c>
+      <c r="E86" t="s">
+        <v>19</v>
+      </c>
+      <c r="F86" t="s">
+        <v>68</v>
+      </c>
+      <c r="G86">
+        <f>G85+($Q85*1000)</f>
+        <v>582000</v>
+      </c>
+      <c r="H86" t="s">
+        <v>19</v>
+      </c>
+      <c r="I86" t="s">
+        <v>68</v>
+      </c>
+      <c r="J86">
+        <f>J85+($Q85*1000)</f>
+        <v>582000</v>
+      </c>
+      <c r="K86" t="s">
+        <v>19</v>
+      </c>
+      <c r="L86" t="s">
+        <v>68</v>
+      </c>
+      <c r="M86">
+        <f>M85+($Q85*1000)</f>
+        <v>582000</v>
+      </c>
+      <c r="N86" t="s">
+        <v>19</v>
+      </c>
+      <c r="O86" t="s">
+        <v>68</v>
+      </c>
+      <c r="P86">
+        <f>P85+1</f>
+        <v>24</v>
+      </c>
+      <c r="Q86">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="87" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A87">
+        <f>A86+($Q86*1000)</f>
+        <v>792000</v>
+      </c>
+      <c r="B87" t="s">
+        <v>69</v>
+      </c>
+      <c r="C87" t="s">
+        <v>66</v>
+      </c>
+      <c r="D87">
+        <f>D86+($Q86*1000)</f>
+        <v>792000</v>
+      </c>
+      <c r="E87" t="s">
+        <v>69</v>
+      </c>
+      <c r="F87" t="s">
+        <v>66</v>
+      </c>
+      <c r="G87">
+        <f>G86+($Q86*1000)</f>
+        <v>792000</v>
+      </c>
+      <c r="H87" t="s">
+        <v>69</v>
+      </c>
+      <c r="I87" t="s">
+        <v>66</v>
+      </c>
+      <c r="J87">
+        <f>J86+($Q86*1000)</f>
+        <v>792000</v>
+      </c>
+      <c r="K87" t="s">
+        <v>69</v>
+      </c>
+      <c r="L87" t="s">
+        <v>66</v>
+      </c>
+      <c r="M87">
+        <f>M86+($Q86*1000)</f>
+        <v>792000</v>
+      </c>
+      <c r="N87" t="s">
+        <v>69</v>
+      </c>
+      <c r="O87" t="s">
+        <v>66</v>
+      </c>
+      <c r="P87">
+        <f>P86+1</f>
+        <v>25</v>
+      </c>
+      <c r="Q87">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="88" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A88">
+        <f>A87+($Q87*1000)</f>
+        <v>812000</v>
+      </c>
+      <c r="B88" t="s">
+        <v>19</v>
+      </c>
+      <c r="C88" t="s">
+        <v>65</v>
+      </c>
+      <c r="D88">
+        <f>D87+($Q87*1000)</f>
+        <v>812000</v>
+      </c>
+      <c r="E88" t="s">
+        <v>19</v>
+      </c>
+      <c r="F88" t="s">
+        <v>65</v>
+      </c>
+      <c r="G88">
+        <f>G87+($Q87*1000)</f>
+        <v>812000</v>
+      </c>
+      <c r="H88" t="s">
+        <v>19</v>
+      </c>
+      <c r="I88" t="s">
+        <v>65</v>
+      </c>
+      <c r="J88">
+        <f>J87+($Q87*1000)</f>
+        <v>812000</v>
+      </c>
+      <c r="K88" t="s">
+        <v>19</v>
+      </c>
+      <c r="L88" t="s">
+        <v>65</v>
+      </c>
+      <c r="M88">
+        <f>M87+($Q87*1000)</f>
+        <v>812000</v>
+      </c>
+      <c r="N88" t="s">
+        <v>19</v>
+      </c>
+      <c r="O88" t="s">
+        <v>65</v>
+      </c>
+      <c r="P88">
+        <f>P87+1</f>
+        <v>26</v>
+      </c>
+      <c r="Q88">
+        <v>10000</v>
       </c>
     </row>
   </sheetData>

--- a/onsets_edit.xlsx
+++ b/onsets_edit.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/brandonwoosnyder/Dropbox/docs-d/00_UCI_2025-2026/02_UCI_Winter_2026/Independent Study Rajna - Music 299/Constrained_PhoneGuide_Score/ScreenTimeScore/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2705C24-35D6-6A40-B3B2-BBAE27ED7F71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64446C2A-F3BB-DC48-9E87-8753A259AF47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1080" yWindow="-18300" windowWidth="30060" windowHeight="15020" xr2:uid="{656903FE-55D6-334E-8317-D02588440573}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="549" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="571" uniqueCount="74">
   <si>
     <t>onset_ms_1</t>
   </si>
@@ -246,6 +246,15 @@
   </si>
   <si>
     <t>bacon01flickersubtle</t>
+  </si>
+  <si>
+    <t>Play</t>
+  </si>
+  <si>
+    <t>Play (with flashes)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Play </t>
   </si>
 </sst>
 </file>
@@ -776,7 +785,140 @@
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
     <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="9">
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color rgb="FF9C0006"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF9C0006"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF9C0006"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF9C0006"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color rgb="FF9C0006"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF9C0006"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF9C0006"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF9C0006"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color rgb="FF9C0006"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF9C0006"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF9C0006"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF9C0006"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color rgb="FF9C0006"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF9C0006"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF9C0006"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF9C0006"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color rgb="FF9C0006"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF9C0006"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF9C0006"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF9C0006"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color rgb="FF9C0006"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF9C0006"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF9C0006"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF9C0006"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color rgb="FF9C0006"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF9C0006"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF9C0006"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF9C0006"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1112,6 +1254,7 @@
     <col min="3" max="3" width="26.6640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="17.83203125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10.83203125" customWidth="1"/>
+    <col min="8" max="8" width="18.83203125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="27.1640625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="17.1640625" bestFit="1" customWidth="1"/>
   </cols>
@@ -2630,12 +2773,18 @@
       <c r="H44" t="s">
         <v>60</v>
       </c>
+      <c r="I44" t="s">
+        <v>73</v>
+      </c>
       <c r="J44">
         <f t="shared" ref="J44:J49" si="6">J43+$Q43*1000</f>
         <v>172000</v>
       </c>
       <c r="K44" t="s">
         <v>60</v>
+      </c>
+      <c r="L44" t="s">
+        <v>71</v>
       </c>
       <c r="M44">
         <f t="shared" ref="M44:M49" si="7">M43+($Q43*1000)</f>
@@ -2683,12 +2832,18 @@
       <c r="H45" t="s">
         <v>62</v>
       </c>
+      <c r="I45" t="s">
+        <v>72</v>
+      </c>
       <c r="J45">
         <f t="shared" si="6"/>
         <v>207000</v>
       </c>
       <c r="K45" t="s">
         <v>62</v>
+      </c>
+      <c r="L45" t="s">
+        <v>72</v>
       </c>
       <c r="M45">
         <f t="shared" si="7"/>
@@ -2736,6 +2891,9 @@
       <c r="H46" t="s">
         <v>62</v>
       </c>
+      <c r="I46" t="s">
+        <v>72</v>
+      </c>
       <c r="J46">
         <f t="shared" si="6"/>
         <v>228000</v>
@@ -3647,6 +3805,9 @@
       <c r="H67" t="s">
         <v>60</v>
       </c>
+      <c r="I67" t="s">
+        <v>71</v>
+      </c>
       <c r="J67">
         <f t="shared" si="10"/>
         <v>310900</v>
@@ -3735,6 +3896,9 @@
       <c r="H69" t="s">
         <v>60</v>
       </c>
+      <c r="I69" t="s">
+        <v>71</v>
+      </c>
       <c r="J69">
         <f t="shared" si="10"/>
         <v>319000</v>
@@ -3823,6 +3987,9 @@
       <c r="K71" t="s">
         <v>60</v>
       </c>
+      <c r="L71" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="72" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A72">
@@ -3832,6 +3999,9 @@
       <c r="B72" t="s">
         <v>60</v>
       </c>
+      <c r="C72" t="s">
+        <v>71</v>
+      </c>
       <c r="D72">
         <f t="shared" si="11"/>
         <v>320850</v>
@@ -3851,6 +4021,9 @@
       <c r="E73" t="s">
         <v>60</v>
       </c>
+      <c r="F73" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="74" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A74">
@@ -3860,6 +4033,9 @@
       <c r="B74" t="s">
         <v>60</v>
       </c>
+      <c r="C74" t="s">
+        <v>71</v>
+      </c>
       <c r="D74">
         <f>$M74</f>
         <v>327000</v>
@@ -3867,6 +4043,9 @@
       <c r="E74" t="s">
         <v>60</v>
       </c>
+      <c r="F74" t="s">
+        <v>71</v>
+      </c>
       <c r="G74">
         <f>$M74</f>
         <v>327000</v>
@@ -3874,12 +4053,18 @@
       <c r="H74" t="s">
         <v>62</v>
       </c>
+      <c r="I74" t="s">
+        <v>72</v>
+      </c>
       <c r="J74">
         <f>$M74</f>
         <v>327000</v>
       </c>
       <c r="K74" t="s">
         <v>60</v>
+      </c>
+      <c r="L74" t="s">
+        <v>71</v>
       </c>
       <c r="M74">
         <f>M69+($Q69*1000)</f>
@@ -3907,6 +4092,9 @@
       <c r="B83" t="s">
         <v>60</v>
       </c>
+      <c r="C83" t="s">
+        <v>71</v>
+      </c>
       <c r="D83">
         <f>$M83</f>
         <v>367000</v>
@@ -3914,6 +4102,9 @@
       <c r="E83" t="s">
         <v>60</v>
       </c>
+      <c r="F83" t="s">
+        <v>71</v>
+      </c>
       <c r="G83">
         <f>$M83</f>
         <v>367000</v>
@@ -3921,12 +4112,18 @@
       <c r="H83" t="s">
         <v>62</v>
       </c>
+      <c r="I83" t="s">
+        <v>72</v>
+      </c>
       <c r="J83">
         <f>$M83</f>
         <v>367000</v>
       </c>
       <c r="K83" t="s">
         <v>62</v>
+      </c>
+      <c r="L83" t="s">
+        <v>72</v>
       </c>
       <c r="M83">
         <f>M74+($Q74*1000)</f>
@@ -3963,6 +4160,9 @@
       <c r="B85" t="s">
         <v>62</v>
       </c>
+      <c r="C85" t="s">
+        <v>72</v>
+      </c>
       <c r="D85">
         <f>$M85</f>
         <v>372000</v>
@@ -3970,6 +4170,9 @@
       <c r="E85" t="s">
         <v>62</v>
       </c>
+      <c r="F85" t="s">
+        <v>72</v>
+      </c>
       <c r="G85">
         <f>$M85</f>
         <v>372000</v>
@@ -3977,12 +4180,18 @@
       <c r="H85" t="s">
         <v>62</v>
       </c>
+      <c r="I85" t="s">
+        <v>72</v>
+      </c>
       <c r="J85">
         <f>$M85</f>
         <v>372000</v>
       </c>
       <c r="K85" t="s">
         <v>62</v>
+      </c>
+      <c r="L85" t="s">
+        <v>72</v>
       </c>
       <c r="M85">
         <f>M83+($Q83*1000)</f>
@@ -4180,6 +4389,11 @@
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="A1:XFD1048576">
+    <cfRule type="containsText" dxfId="8" priority="1" operator="containsText" text="bacon">
+      <formula>NOT(ISERROR(SEARCH("bacon",A1)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/onsets_edit.xlsx
+++ b/onsets_edit.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/brandonwoosnyder/Dropbox/docs-d/00_UCI_2025-2026/02_UCI_Winter_2026/Independent Study Rajna - Music 299/Constrained_PhoneGuide_Score/ScreenTimeScore/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64446C2A-F3BB-DC48-9E87-8753A259AF47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7118A6A-38C8-2A46-885D-F7E974E12A82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1080" yWindow="-18300" windowWidth="30060" windowHeight="15020" xr2:uid="{656903FE-55D6-334E-8317-D02588440573}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="571" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="571" uniqueCount="73">
   <si>
     <t>onset_ms_1</t>
   </si>
@@ -165,9 +165,6 @@
   </si>
   <si>
     <t>PICK UP INST.</t>
-  </si>
-  <si>
-    <t>Tacet 1"</t>
   </si>
   <si>
     <t>needs to be at least 6 seconds</t>
@@ -785,129 +782,7 @@
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
     <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="9">
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color rgb="FF9C0006"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF9C0006"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF9C0006"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF9C0006"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color rgb="FF9C0006"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF9C0006"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF9C0006"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF9C0006"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color rgb="FF9C0006"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF9C0006"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF9C0006"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF9C0006"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color rgb="FF9C0006"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF9C0006"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF9C0006"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF9C0006"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color rgb="FF9C0006"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF9C0006"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF9C0006"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF9C0006"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color rgb="FF9C0006"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF9C0006"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF9C0006"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF9C0006"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color rgb="FF9C0006"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF9C0006"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF9C0006"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF9C0006"/>
-        </bottom>
-      </border>
-    </dxf>
+  <dxfs count="1">
     <dxf>
       <font>
         <color rgb="FF9C5700"/>
@@ -1251,6 +1126,7 @@
   <dimension ref="A1:S88"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
+    <col min="2" max="2" width="18.83203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="26.6640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="17.83203125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10.83203125" customWidth="1"/>
@@ -1805,31 +1681,31 @@
         <v>10000</v>
       </c>
       <c r="B12" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D12">
         <v>10000</v>
       </c>
       <c r="E12" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G12">
         <v>10000</v>
       </c>
       <c r="H12" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J12">
         <v>10000</v>
       </c>
       <c r="K12" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="M12">
         <v>10000</v>
       </c>
       <c r="N12" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="P12">
         <f>P2+1</f>
@@ -1845,35 +1721,35 @@
         <v>30000</v>
       </c>
       <c r="B13" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D13">
         <f>D12+($Q12*1000)</f>
         <v>30000</v>
       </c>
       <c r="E13" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G13">
         <f>G12+($Q12*1000)</f>
         <v>30000</v>
       </c>
       <c r="H13" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J13">
         <f>J12+($Q12*1000)</f>
         <v>30000</v>
       </c>
       <c r="K13" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="M13">
         <f>M12+($Q12*1000)</f>
         <v>30000</v>
       </c>
       <c r="N13" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="P13">
         <f>P12+1</f>
@@ -1892,7 +1768,7 @@
         <v>19</v>
       </c>
       <c r="C14" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D14">
         <f>D13+($Q13*1000)</f>
@@ -1902,7 +1778,7 @@
         <v>19</v>
       </c>
       <c r="F14" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G14">
         <f>G13+($Q13*1000)</f>
@@ -1912,7 +1788,7 @@
         <v>19</v>
       </c>
       <c r="I14" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J14">
         <f>J13+($Q13*1000)</f>
@@ -1922,7 +1798,7 @@
         <v>19</v>
       </c>
       <c r="L14" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="M14">
         <f>M13+($Q13*1000)</f>
@@ -1932,7 +1808,7 @@
         <v>19</v>
       </c>
       <c r="O14" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="P14">
         <f>P13+1</f>
@@ -2692,7 +2568,7 @@
         <v>19</v>
       </c>
       <c r="C43" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="D43">
         <f>D40+($Q40*1000)</f>
@@ -2702,7 +2578,7 @@
         <v>19</v>
       </c>
       <c r="F43" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G43">
         <f>G40+Q40*1000</f>
@@ -2732,7 +2608,7 @@
         <v>19</v>
       </c>
       <c r="O43" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="P43">
         <f>P40+1</f>
@@ -2742,7 +2618,7 @@
         <v>6</v>
       </c>
       <c r="R43" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="44" spans="1:18" x14ac:dyDescent="0.2">
@@ -2754,7 +2630,7 @@
         <v>19</v>
       </c>
       <c r="C44" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D44">
         <f t="shared" ref="D44:D49" si="4">D43+($Q43*1000)</f>
@@ -2764,27 +2640,27 @@
         <v>19</v>
       </c>
       <c r="F44" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G44">
         <f t="shared" ref="G44:G49" si="5">G43+$Q43*1000</f>
         <v>172000</v>
       </c>
       <c r="H44" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I44" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="J44">
         <f t="shared" ref="J44:J49" si="6">J43+$Q43*1000</f>
         <v>172000</v>
       </c>
       <c r="K44" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="L44" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="M44">
         <f t="shared" ref="M44:M49" si="7">M43+($Q43*1000)</f>
@@ -2794,7 +2670,7 @@
         <v>19</v>
       </c>
       <c r="O44" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="P44">
         <f>P43+1</f>
@@ -2813,7 +2689,7 @@
         <v>19</v>
       </c>
       <c r="C45" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D45">
         <f t="shared" si="4"/>
@@ -2823,27 +2699,27 @@
         <v>19</v>
       </c>
       <c r="F45" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G45">
         <f t="shared" si="5"/>
         <v>207000</v>
       </c>
       <c r="H45" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="I45" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J45">
         <f t="shared" si="6"/>
         <v>207000</v>
       </c>
       <c r="K45" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="L45" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="M45">
         <f t="shared" si="7"/>
@@ -2853,7 +2729,7 @@
         <v>19</v>
       </c>
       <c r="O45" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="P45">
         <f t="shared" ref="P45:P49" si="8">P44+1</f>
@@ -2872,7 +2748,7 @@
         <v>19</v>
       </c>
       <c r="C46" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D46">
         <f t="shared" si="4"/>
@@ -2882,17 +2758,17 @@
         <v>19</v>
       </c>
       <c r="F46" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G46">
         <f t="shared" si="5"/>
         <v>228000</v>
       </c>
       <c r="H46" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="I46" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J46">
         <f t="shared" si="6"/>
@@ -2902,7 +2778,7 @@
         <v>31</v>
       </c>
       <c r="L46" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="M46">
         <f t="shared" si="7"/>
@@ -2912,7 +2788,7 @@
         <v>19</v>
       </c>
       <c r="O46" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="P46">
         <f t="shared" si="8"/>
@@ -2931,7 +2807,7 @@
         <v>19</v>
       </c>
       <c r="C47" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D47">
         <f t="shared" si="4"/>
@@ -2941,7 +2817,7 @@
         <v>19</v>
       </c>
       <c r="F47" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G47">
         <f t="shared" si="5"/>
@@ -2951,7 +2827,7 @@
         <v>31</v>
       </c>
       <c r="I47" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J47">
         <f t="shared" si="6"/>
@@ -2961,7 +2837,7 @@
         <v>31</v>
       </c>
       <c r="L47" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="M47">
         <f t="shared" si="7"/>
@@ -2971,7 +2847,7 @@
         <v>19</v>
       </c>
       <c r="O47" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="P47">
         <f t="shared" si="8"/>
@@ -2990,7 +2866,7 @@
         <v>19</v>
       </c>
       <c r="C48" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D48">
         <f t="shared" si="4"/>
@@ -3000,7 +2876,7 @@
         <v>19</v>
       </c>
       <c r="F48" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G48">
         <f t="shared" si="5"/>
@@ -3010,7 +2886,7 @@
         <v>31</v>
       </c>
       <c r="I48" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="J48">
         <f t="shared" si="6"/>
@@ -3020,7 +2896,7 @@
         <v>31</v>
       </c>
       <c r="L48" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="M48">
         <f t="shared" si="7"/>
@@ -3030,7 +2906,7 @@
         <v>19</v>
       </c>
       <c r="O48" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="P48">
         <f t="shared" si="8"/>
@@ -3059,7 +2935,7 @@
         <v>31</v>
       </c>
       <c r="F49" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G49">
         <f t="shared" si="5"/>
@@ -3108,7 +2984,7 @@
         <v>19</v>
       </c>
       <c r="F50" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G50">
         <f t="shared" ref="G50:G66" si="9">G49+($S$2)</f>
@@ -3140,7 +3016,7 @@
         <v>31</v>
       </c>
       <c r="F51" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G51">
         <f t="shared" si="9"/>
@@ -3172,7 +3048,7 @@
         <v>19</v>
       </c>
       <c r="F52" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G52">
         <f t="shared" si="9"/>
@@ -3204,7 +3080,7 @@
         <v>31</v>
       </c>
       <c r="F53" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G53">
         <f t="shared" si="9"/>
@@ -3236,7 +3112,7 @@
         <v>19</v>
       </c>
       <c r="F54" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G54">
         <f t="shared" si="9"/>
@@ -3278,7 +3154,7 @@
         <v>31</v>
       </c>
       <c r="F55" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G55">
         <f t="shared" si="9"/>
@@ -3327,7 +3203,7 @@
         <v>19</v>
       </c>
       <c r="F56" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G56">
         <f t="shared" si="9"/>
@@ -3359,7 +3235,7 @@
         <v>31</v>
       </c>
       <c r="F57" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G57">
         <f t="shared" si="9"/>
@@ -3391,7 +3267,7 @@
         <v>19</v>
       </c>
       <c r="C58" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D58">
         <f t="shared" si="11"/>
@@ -3401,7 +3277,7 @@
         <v>19</v>
       </c>
       <c r="F58" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G58">
         <f t="shared" si="9"/>
@@ -3433,7 +3309,7 @@
         <v>31</v>
       </c>
       <c r="C59" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D59">
         <f t="shared" si="11"/>
@@ -3443,7 +3319,7 @@
         <v>31</v>
       </c>
       <c r="F59" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G59">
         <f t="shared" si="9"/>
@@ -3475,7 +3351,7 @@
         <v>19</v>
       </c>
       <c r="C60" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D60">
         <f t="shared" si="11"/>
@@ -3485,7 +3361,7 @@
         <v>19</v>
       </c>
       <c r="F60" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G60">
         <f t="shared" si="9"/>
@@ -3517,7 +3393,7 @@
         <v>31</v>
       </c>
       <c r="C61" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D61">
         <f t="shared" si="11"/>
@@ -3527,7 +3403,7 @@
         <v>31</v>
       </c>
       <c r="F61" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G61">
         <f t="shared" si="9"/>
@@ -3559,7 +3435,7 @@
         <v>19</v>
       </c>
       <c r="C62" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D62">
         <f t="shared" si="11"/>
@@ -3569,7 +3445,7 @@
         <v>19</v>
       </c>
       <c r="F62" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G62">
         <f t="shared" si="9"/>
@@ -3599,7 +3475,7 @@
         <v>19</v>
       </c>
       <c r="O62" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="P62">
         <f>P55+1</f>
@@ -3618,7 +3494,7 @@
         <v>31</v>
       </c>
       <c r="C63" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D63">
         <f t="shared" si="11"/>
@@ -3628,7 +3504,7 @@
         <v>31</v>
       </c>
       <c r="F63" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G63">
         <f t="shared" si="9"/>
@@ -3660,7 +3536,7 @@
         <v>19</v>
       </c>
       <c r="C64" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D64">
         <f t="shared" si="11"/>
@@ -3670,7 +3546,7 @@
         <v>19</v>
       </c>
       <c r="F64" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G64">
         <f t="shared" si="9"/>
@@ -3702,7 +3578,7 @@
         <v>31</v>
       </c>
       <c r="C65" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D65">
         <f t="shared" si="11"/>
@@ -3712,7 +3588,7 @@
         <v>31</v>
       </c>
       <c r="F65" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G65">
         <f t="shared" si="9"/>
@@ -3722,7 +3598,7 @@
         <v>31</v>
       </c>
       <c r="I65" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J65">
         <f t="shared" si="10"/>
@@ -3744,7 +3620,7 @@
         <v>19</v>
       </c>
       <c r="C66" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D66">
         <f t="shared" si="11"/>
@@ -3754,7 +3630,7 @@
         <v>19</v>
       </c>
       <c r="F66" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G66">
         <f t="shared" si="9"/>
@@ -3786,7 +3662,7 @@
         <v>31</v>
       </c>
       <c r="C67" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D67">
         <f t="shared" si="11"/>
@@ -3796,17 +3672,17 @@
         <v>31</v>
       </c>
       <c r="F67" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G67">
         <f>G66+($S$2)</f>
         <v>310000</v>
       </c>
       <c r="H67" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I67" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="J67">
         <f t="shared" si="10"/>
@@ -3845,7 +3721,7 @@
         <v>19</v>
       </c>
       <c r="C68" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D68">
         <f t="shared" si="11"/>
@@ -3855,7 +3731,7 @@
         <v>19</v>
       </c>
       <c r="F68" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J68">
         <f t="shared" si="10"/>
@@ -3877,7 +3753,7 @@
         <v>31</v>
       </c>
       <c r="C69" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D69">
         <f t="shared" si="11"/>
@@ -3887,17 +3763,17 @@
         <v>31</v>
       </c>
       <c r="F69" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G69">
         <f>G67+$Q67*1000</f>
         <v>320000</v>
       </c>
       <c r="H69" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I69" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="J69">
         <f t="shared" si="10"/>
@@ -3917,7 +3793,7 @@
         <v>19</v>
       </c>
       <c r="O69" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="P69">
         <f>P67+1</f>
@@ -3936,7 +3812,7 @@
         <v>19</v>
       </c>
       <c r="C70" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D70">
         <f t="shared" si="11"/>
@@ -3946,7 +3822,7 @@
         <v>19</v>
       </c>
       <c r="F70" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J70">
         <f t="shared" si="10"/>
@@ -3968,7 +3844,7 @@
         <v>31</v>
       </c>
       <c r="C71" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D71">
         <f t="shared" si="11"/>
@@ -3978,17 +3854,17 @@
         <v>31</v>
       </c>
       <c r="F71" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J71">
         <f>J70+($S$2*(1+$R$2))</f>
         <v>327100</v>
       </c>
       <c r="K71" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="L71" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="72" spans="1:17" x14ac:dyDescent="0.2">
@@ -3997,10 +3873,10 @@
         <v>331600</v>
       </c>
       <c r="B72" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C72" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D72">
         <f t="shared" si="11"/>
@@ -4010,7 +3886,7 @@
         <v>19</v>
       </c>
       <c r="F72" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="73" spans="1:17" x14ac:dyDescent="0.2">
@@ -4019,10 +3895,10 @@
         <v>324800</v>
       </c>
       <c r="E73" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F73" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="74" spans="1:17" x14ac:dyDescent="0.2">
@@ -4031,40 +3907,40 @@
         <v>327000</v>
       </c>
       <c r="B74" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C74" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D74">
         <f>$M74</f>
         <v>327000</v>
       </c>
       <c r="E74" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F74" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G74">
         <f>$M74</f>
         <v>327000</v>
       </c>
       <c r="H74" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="I74" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J74">
         <f>$M74</f>
         <v>327000</v>
       </c>
       <c r="K74" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="L74" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="M74">
         <f>M69+($Q69*1000)</f>
@@ -4074,7 +3950,7 @@
         <v>19</v>
       </c>
       <c r="O74" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="P74">
         <f>P69+1</f>
@@ -4090,40 +3966,40 @@
         <v>367000</v>
       </c>
       <c r="B83" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C83" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D83">
         <f>$M83</f>
         <v>367000</v>
       </c>
       <c r="E83" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F83" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G83">
         <f>$M83</f>
         <v>367000</v>
       </c>
       <c r="H83" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="I83" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J83">
         <f>$M83</f>
         <v>367000</v>
       </c>
       <c r="K83" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="L83" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="M83">
         <f>M74+($Q74*1000)</f>
@@ -4149,7 +4025,7 @@
         <v>369500</v>
       </c>
       <c r="E84" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="85" spans="1:17" x14ac:dyDescent="0.2">
@@ -4158,40 +4034,40 @@
         <v>372000</v>
       </c>
       <c r="B85" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C85" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D85">
         <f>$M85</f>
         <v>372000</v>
       </c>
       <c r="E85" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F85" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G85">
         <f>$M85</f>
         <v>372000</v>
       </c>
       <c r="H85" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="I85" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J85">
         <f>$M85</f>
         <v>372000</v>
       </c>
       <c r="K85" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="L85" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="M85">
         <f>M83+($Q83*1000)</f>
@@ -4201,7 +4077,7 @@
         <v>19</v>
       </c>
       <c r="O85" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="P85">
         <f>P83+1</f>
@@ -4220,7 +4096,7 @@
         <v>19</v>
       </c>
       <c r="C86" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D86">
         <f>D85+($Q85*1000)</f>
@@ -4230,7 +4106,7 @@
         <v>19</v>
       </c>
       <c r="F86" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G86">
         <f>G85+($Q85*1000)</f>
@@ -4240,7 +4116,7 @@
         <v>19</v>
       </c>
       <c r="I86" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="J86">
         <f>J85+($Q85*1000)</f>
@@ -4250,7 +4126,7 @@
         <v>19</v>
       </c>
       <c r="L86" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="M86">
         <f>M85+($Q85*1000)</f>
@@ -4260,7 +4136,7 @@
         <v>19</v>
       </c>
       <c r="O86" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="P86">
         <f>P85+1</f>
@@ -4276,50 +4152,50 @@
         <v>792000</v>
       </c>
       <c r="B87" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C87" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D87">
         <f>D86+($Q86*1000)</f>
         <v>792000</v>
       </c>
       <c r="E87" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F87" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G87">
         <f>G86+($Q86*1000)</f>
         <v>792000</v>
       </c>
       <c r="H87" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I87" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="J87">
         <f>J86+($Q86*1000)</f>
         <v>792000</v>
       </c>
       <c r="K87" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="L87" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="M87">
         <f>M86+($Q86*1000)</f>
         <v>792000</v>
       </c>
       <c r="N87" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="O87" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="P87">
         <f>P86+1</f>
@@ -4338,7 +4214,7 @@
         <v>19</v>
       </c>
       <c r="C88" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D88">
         <f>D87+($Q87*1000)</f>
@@ -4348,7 +4224,7 @@
         <v>19</v>
       </c>
       <c r="F88" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G88">
         <f>G87+($Q87*1000)</f>
@@ -4358,7 +4234,7 @@
         <v>19</v>
       </c>
       <c r="I88" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J88">
         <f>J87+($Q87*1000)</f>
@@ -4368,7 +4244,7 @@
         <v>19</v>
       </c>
       <c r="L88" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="M88">
         <f>M87+($Q87*1000)</f>
@@ -4378,7 +4254,7 @@
         <v>19</v>
       </c>
       <c r="O88" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="P88">
         <f>P87+1</f>
@@ -4390,7 +4266,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="containsText" dxfId="8" priority="1" operator="containsText" text="bacon">
+    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="bacon">
       <formula>NOT(ISERROR(SEARCH("bacon",A1)))</formula>
     </cfRule>
   </conditionalFormatting>

--- a/onsets_edit.xlsx
+++ b/onsets_edit.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/brandonwoosnyder/Dropbox/docs-d/00_UCI_2025-2026/02_UCI_Winter_2026/Independent Study Rajna - Music 299/Constrained_PhoneGuide_Score/ScreenTimeScore/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7118A6A-38C8-2A46-885D-F7E974E12A82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3386BBCA-04B7-D344-A5CC-AE710CBEC174}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1080" yWindow="-18300" windowWidth="30060" windowHeight="15020" xr2:uid="{656903FE-55D6-334E-8317-D02588440573}"/>
+    <workbookView xWindow="-2160" yWindow="-23220" windowWidth="43080" windowHeight="19580" xr2:uid="{656903FE-55D6-334E-8317-D02588440573}"/>
   </bookViews>
   <sheets>
     <sheet name="onsets" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="571" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="563" uniqueCount="84">
   <si>
     <t>onset_ms_1</t>
   </si>
@@ -149,15 +149,6 @@
     <t>Phone Up (hold!)</t>
   </si>
   <si>
-    <t>Phone Down</t>
-  </si>
-  <si>
-    <t>Phone Up</t>
-  </si>
-  <si>
-    <t>Tacet 12"</t>
-  </si>
-  <si>
     <t>Tacet 10"</t>
   </si>
   <si>
@@ -209,9 +200,6 @@
     <t>Tacet 15"</t>
   </si>
   <si>
-    <t>Phone down and PICK UP INST.</t>
-  </si>
-  <si>
     <t>bacon01</t>
   </si>
   <si>
@@ -227,18 +215,6 @@
     <t>Tacet 6"</t>
   </si>
   <si>
-    <t>open final measure</t>
-  </si>
-  <si>
-    <t>flickering measure</t>
-  </si>
-  <si>
-    <t>OPEN FLASH</t>
-  </si>
-  <si>
-    <t>OPEN FADE AND REST</t>
-  </si>
-  <si>
     <t>bacon01flickerheavy</t>
   </si>
   <si>
@@ -252,6 +228,65 @@
   </si>
   <si>
     <t xml:space="preserve">Play </t>
+  </si>
+  <si>
+    <t>Hold Phone Up: 10</t>
+  </si>
+  <si>
+    <t>Hold Phone Up: 9</t>
+  </si>
+  <si>
+    <t>Hold Phone Up: 8</t>
+  </si>
+  <si>
+    <t>Hold Phone Up: 7</t>
+  </si>
+  <si>
+    <t>Hold Phone Up: 6</t>
+  </si>
+  <si>
+    <t>Hold Phone Up: 5</t>
+  </si>
+  <si>
+    <t>Hold Phone Up: 4</t>
+  </si>
+  <si>
+    <t>Hold Phone Up: 3</t>
+  </si>
+  <si>
+    <t>Hold Phone Up: 2</t>
+  </si>
+  <si>
+    <t>Hold Phone Up: 1</t>
+  </si>
+  <si>
+    <t>Gaze at Image</t>
+  </si>
+  <si>
+    <t>Phone Down (brief!)</t>
+  </si>
+  <si>
+    <t>Phone Up (brief!)</t>
+  </si>
+  <si>
+    <t>(Play, then end)</t>
+  </si>
+  <si>
+    <t>Play (with flashes) 
+(eventually fade out)</t>
+  </si>
+  <si>
+    <t>IGNORE PHONE 
+(play openly)</t>
+  </si>
+  <si>
+    <t>Phone Up (long)</t>
+  </si>
+  <si>
+    <t>Phone Down (3")</t>
+  </si>
+  <si>
+    <t>Phone Up (3")</t>
   </si>
 </sst>
 </file>
@@ -735,8 +770,11 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1123,7 +1161,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E707C8EF-5282-2B42-BB2D-C2C257FF5AA3}">
-  <dimension ref="A1:S88"/>
+  <dimension ref="A1:S75"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="18.83203125" bestFit="1" customWidth="1"/>
@@ -1132,7 +1170,8 @@
     <col min="7" max="7" width="10.83203125" customWidth="1"/>
     <col min="8" max="8" width="18.83203125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="27.1640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="17.1640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="33.1640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="19" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.2">
@@ -1202,7 +1241,7 @@
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>20</v>
+        <v>65</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -1261,7 +1300,7 @@
         <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>21</v>
+        <v>66</v>
       </c>
       <c r="D3">
         <v>1000</v>
@@ -1308,7 +1347,7 @@
         <v>19</v>
       </c>
       <c r="C4" t="s">
-        <v>22</v>
+        <v>67</v>
       </c>
       <c r="D4">
         <v>2000</v>
@@ -1355,7 +1394,7 @@
         <v>19</v>
       </c>
       <c r="C5" t="s">
-        <v>23</v>
+        <v>68</v>
       </c>
       <c r="D5">
         <v>3000</v>
@@ -1402,7 +1441,7 @@
         <v>19</v>
       </c>
       <c r="C6" t="s">
-        <v>24</v>
+        <v>69</v>
       </c>
       <c r="D6">
         <v>4000</v>
@@ -1449,7 +1488,7 @@
         <v>19</v>
       </c>
       <c r="C7" t="s">
-        <v>25</v>
+        <v>70</v>
       </c>
       <c r="D7">
         <v>5000</v>
@@ -1496,7 +1535,7 @@
         <v>19</v>
       </c>
       <c r="C8" t="s">
-        <v>26</v>
+        <v>71</v>
       </c>
       <c r="D8">
         <v>6000</v>
@@ -1543,7 +1582,7 @@
         <v>19</v>
       </c>
       <c r="C9" t="s">
-        <v>27</v>
+        <v>72</v>
       </c>
       <c r="D9">
         <v>7000</v>
@@ -1590,7 +1629,7 @@
         <v>19</v>
       </c>
       <c r="C10" t="s">
-        <v>28</v>
+        <v>73</v>
       </c>
       <c r="D10">
         <v>8000</v>
@@ -1637,7 +1676,7 @@
         <v>19</v>
       </c>
       <c r="C11" t="s">
-        <v>29</v>
+        <v>74</v>
       </c>
       <c r="D11">
         <v>9000</v>
@@ -1681,31 +1720,46 @@
         <v>10000</v>
       </c>
       <c r="B12" t="s">
-        <v>62</v>
+        <v>58</v>
+      </c>
+      <c r="C12" t="s">
+        <v>75</v>
       </c>
       <c r="D12">
         <v>10000</v>
       </c>
       <c r="E12" t="s">
-        <v>62</v>
+        <v>58</v>
+      </c>
+      <c r="F12" t="s">
+        <v>75</v>
       </c>
       <c r="G12">
         <v>10000</v>
       </c>
       <c r="H12" t="s">
-        <v>62</v>
+        <v>58</v>
+      </c>
+      <c r="I12" t="s">
+        <v>75</v>
       </c>
       <c r="J12">
         <v>10000</v>
       </c>
       <c r="K12" t="s">
-        <v>62</v>
+        <v>58</v>
+      </c>
+      <c r="L12" t="s">
+        <v>75</v>
       </c>
       <c r="M12">
         <v>10000</v>
       </c>
       <c r="N12" t="s">
-        <v>62</v>
+        <v>58</v>
+      </c>
+      <c r="O12" t="s">
+        <v>75</v>
       </c>
       <c r="P12">
         <f>P2+1</f>
@@ -1721,35 +1775,50 @@
         <v>30000</v>
       </c>
       <c r="B13" t="s">
-        <v>69</v>
+        <v>61</v>
+      </c>
+      <c r="C13" t="s">
+        <v>75</v>
       </c>
       <c r="D13">
         <f>D12+($Q12*1000)</f>
         <v>30000</v>
       </c>
       <c r="E13" t="s">
-        <v>69</v>
+        <v>61</v>
+      </c>
+      <c r="F13" t="s">
+        <v>75</v>
       </c>
       <c r="G13">
         <f>G12+($Q12*1000)</f>
         <v>30000</v>
       </c>
       <c r="H13" t="s">
-        <v>69</v>
+        <v>61</v>
+      </c>
+      <c r="I13" t="s">
+        <v>75</v>
       </c>
       <c r="J13">
         <f>J12+($Q12*1000)</f>
         <v>30000</v>
       </c>
       <c r="K13" t="s">
-        <v>69</v>
+        <v>61</v>
+      </c>
+      <c r="L13" t="s">
+        <v>75</v>
       </c>
       <c r="M13">
         <f>M12+($Q12*1000)</f>
         <v>30000</v>
       </c>
       <c r="N13" t="s">
-        <v>69</v>
+        <v>61</v>
+      </c>
+      <c r="O13" t="s">
+        <v>75</v>
       </c>
       <c r="P13">
         <f>P12+1</f>
@@ -1768,7 +1837,7 @@
         <v>19</v>
       </c>
       <c r="C14" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="D14">
         <f>D13+($Q13*1000)</f>
@@ -1778,7 +1847,7 @@
         <v>19</v>
       </c>
       <c r="F14" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="G14">
         <f>G13+($Q13*1000)</f>
@@ -1788,7 +1857,7 @@
         <v>19</v>
       </c>
       <c r="I14" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="J14">
         <f>J13+($Q13*1000)</f>
@@ -1798,7 +1867,7 @@
         <v>19</v>
       </c>
       <c r="L14" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="M14">
         <f>M13+($Q13*1000)</f>
@@ -1808,7 +1877,7 @@
         <v>19</v>
       </c>
       <c r="O14" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="P14">
         <f>P13+1</f>
@@ -2048,7 +2117,7 @@
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.2">
       <c r="G22">
-        <f t="shared" ref="G22:G40" si="2">G21+($S$2)</f>
+        <f t="shared" ref="G22:G31" si="2">G21+($S$2)</f>
         <v>84000</v>
       </c>
       <c r="H22" t="s">
@@ -2209,6 +2278,16 @@
       <c r="I28" t="s">
         <v>34</v>
       </c>
+      <c r="J28">
+        <f>M28</f>
+        <v>108000</v>
+      </c>
+      <c r="K28" t="s">
+        <v>31</v>
+      </c>
+      <c r="L28" t="s">
+        <v>37</v>
+      </c>
       <c r="M28">
         <f>M21+($Q21*1000)</f>
         <v>108000</v>
@@ -2224,7 +2303,7 @@
         <v>7</v>
       </c>
       <c r="Q28">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.2">
@@ -2238,6 +2317,16 @@
       <c r="I29" t="s">
         <v>32</v>
       </c>
+      <c r="J29">
+        <f>J27+(11000)</f>
+        <v>115600</v>
+      </c>
+      <c r="K29" t="s">
+        <v>19</v>
+      </c>
+      <c r="L29" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.2">
       <c r="G30">
@@ -2251,14 +2340,14 @@
         <v>34</v>
       </c>
       <c r="J30">
-        <f>J27+(11000)</f>
-        <v>115600</v>
+        <f>J29+1000</f>
+        <v>116600</v>
       </c>
       <c r="K30" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="L30" t="s">
-        <v>38</v>
+        <v>77</v>
       </c>
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.2">
@@ -2270,57 +2359,67 @@
         <v>31</v>
       </c>
       <c r="I31" t="s">
-        <v>32</v>
+        <v>83</v>
       </c>
       <c r="J31">
-        <f>J30+2000</f>
+        <f>J30+1000</f>
         <v>117600</v>
       </c>
       <c r="K31" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="L31" t="s">
-        <v>39</v>
+        <v>76</v>
       </c>
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.2">
       <c r="G32">
-        <f t="shared" si="2"/>
-        <v>124000</v>
+        <f>G31+($S$2*0.75)</f>
+        <v>123000</v>
       </c>
       <c r="H32" t="s">
         <v>19</v>
       </c>
       <c r="I32" t="s">
-        <v>34</v>
+        <v>82</v>
       </c>
       <c r="J32">
-        <f>J31+4000</f>
-        <v>121600</v>
+        <f>G32</f>
+        <v>123000</v>
       </c>
       <c r="K32" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="L32" t="s">
-        <v>38</v>
+        <v>83</v>
       </c>
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.2">
       <c r="G33">
-        <f t="shared" si="2"/>
-        <v>128000</v>
+        <f>G32+($S$2*0.75)</f>
+        <v>126000</v>
       </c>
       <c r="H33" t="s">
         <v>31</v>
       </c>
       <c r="I33" t="s">
-        <v>32</v>
+        <v>83</v>
+      </c>
+      <c r="J33">
+        <f>G33</f>
+        <v>126000</v>
+      </c>
+      <c r="K33" t="s">
+        <v>19</v>
+      </c>
+      <c r="L33" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="34" spans="1:18" x14ac:dyDescent="0.2">
       <c r="G34">
-        <f t="shared" si="2"/>
-        <v>132000</v>
+        <f>G33+($S$2*0.75)</f>
+        <v>129000</v>
       </c>
       <c r="H34" t="s">
         <v>19</v>
@@ -2329,1943 +2428,1806 @@
         <v>34</v>
       </c>
       <c r="J34">
-        <f>J32+11000</f>
-        <v>132600</v>
+        <f>G34</f>
+        <v>129000</v>
       </c>
       <c r="K34" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="L34" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="35" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A35">
         <f>A28+($Q28*1000)</f>
-        <v>136000</v>
+        <v>133000</v>
       </c>
       <c r="B35" t="s">
         <v>19</v>
       </c>
       <c r="C35" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D35">
         <f>D28+($Q28*1000)</f>
-        <v>136000</v>
+        <v>133000</v>
       </c>
       <c r="E35" t="s">
         <v>19</v>
       </c>
       <c r="F35" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G35">
-        <f t="shared" si="2"/>
-        <v>136000</v>
+        <f>G34+($S$2)</f>
+        <v>133000</v>
       </c>
       <c r="H35" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="I35" t="s">
-        <v>32</v>
+        <v>39</v>
+      </c>
+      <c r="J35">
+        <f>J34+($S$2)</f>
+        <v>133000</v>
+      </c>
+      <c r="K35" t="s">
+        <v>31</v>
+      </c>
+      <c r="L35" t="s">
+        <v>77</v>
       </c>
       <c r="M35">
         <f>M28+($Q28*1000)</f>
-        <v>136000</v>
+        <v>133000</v>
       </c>
       <c r="N35" t="s">
         <v>19</v>
       </c>
       <c r="O35" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="P35">
         <f>P28+1</f>
         <v>8</v>
       </c>
       <c r="Q35">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="36" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="G36">
-        <f t="shared" si="2"/>
-        <v>140000</v>
-      </c>
-      <c r="H36" t="s">
-        <v>19</v>
-      </c>
-      <c r="I36" t="s">
-        <v>34</v>
-      </c>
       <c r="J36">
-        <f>G36</f>
-        <v>140000</v>
+        <f>J35+1000</f>
+        <v>134000</v>
       </c>
       <c r="K36" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="L36" t="s">
-        <v>32</v>
+        <v>76</v>
       </c>
     </row>
     <row r="37" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="G37">
-        <f>G36+($S$2)</f>
-        <v>144000</v>
-      </c>
-      <c r="H37" t="s">
-        <v>31</v>
-      </c>
-      <c r="I37" t="s">
-        <v>32</v>
-      </c>
       <c r="J37">
-        <f>J36+($S$2)</f>
-        <v>144000</v>
+        <f>J36+1000</f>
+        <v>135000</v>
       </c>
       <c r="K37" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="L37" t="s">
-        <v>34</v>
+        <v>77</v>
       </c>
     </row>
     <row r="38" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A38">
+        <f>A35+($Q35*1000)</f>
+        <v>141000</v>
+      </c>
+      <c r="B38" t="s">
+        <v>19</v>
+      </c>
+      <c r="C38" t="s">
+        <v>59</v>
+      </c>
+      <c r="D38">
+        <f>D35+($Q35*1000)</f>
+        <v>141000</v>
+      </c>
+      <c r="E38" t="s">
+        <v>19</v>
+      </c>
+      <c r="F38" t="s">
+        <v>59</v>
+      </c>
       <c r="G38">
-        <f>G37+($S$2)</f>
-        <v>148000</v>
+        <f>G35+Q35*1000</f>
+        <v>141000</v>
       </c>
       <c r="H38" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="I38" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="J38">
-        <f>J37+($S$2)</f>
-        <v>148000</v>
+        <f>J37+6000</f>
+        <v>141000</v>
       </c>
       <c r="K38" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="L38" t="s">
-        <v>32</v>
+        <v>40</v>
+      </c>
+      <c r="M38">
+        <f>M35+($Q35*1000)</f>
+        <v>141000</v>
+      </c>
+      <c r="N38" t="s">
+        <v>19</v>
+      </c>
+      <c r="O38" t="s">
+        <v>59</v>
+      </c>
+      <c r="P38">
+        <f>P35+1</f>
+        <v>9</v>
+      </c>
+      <c r="Q38">
+        <v>6</v>
+      </c>
+      <c r="R38" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="39" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A39">
+        <f t="shared" ref="A39:A44" si="3">A38+($Q38*1000)</f>
+        <v>147000</v>
+      </c>
+      <c r="B39" t="s">
+        <v>19</v>
+      </c>
+      <c r="C39" t="s">
+        <v>42</v>
+      </c>
+      <c r="D39">
+        <f t="shared" ref="D39:D44" si="4">D38+($Q38*1000)</f>
+        <v>147000</v>
+      </c>
+      <c r="E39" t="s">
+        <v>19</v>
+      </c>
+      <c r="F39" t="s">
+        <v>42</v>
+      </c>
       <c r="G39">
-        <f t="shared" si="2"/>
-        <v>152000</v>
+        <f>G38+$Q38*1000</f>
+        <v>147000</v>
       </c>
       <c r="H39" t="s">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="I39" t="s">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="J39">
-        <f>J38+($S$2)</f>
-        <v>152000</v>
+        <f>J38+$Q38*1000</f>
+        <v>147000</v>
       </c>
       <c r="K39" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="L39" t="s">
-        <v>34</v>
+        <v>62</v>
+      </c>
+      <c r="M39">
+        <f t="shared" ref="M39:M44" si="5">M38+($Q38*1000)</f>
+        <v>147000</v>
+      </c>
+      <c r="N39" t="s">
+        <v>19</v>
+      </c>
+      <c r="O39" t="s">
+        <v>42</v>
+      </c>
+      <c r="P39">
+        <f>P38+1</f>
+        <v>10</v>
+      </c>
+      <c r="Q39">
+        <v>35</v>
       </c>
     </row>
     <row r="40" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A40">
-        <f>A35+($Q35*1000)</f>
-        <v>148000</v>
+        <f>A39+($Q39*1000)</f>
+        <v>182000</v>
       </c>
       <c r="B40" t="s">
         <v>19</v>
       </c>
       <c r="C40" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D40">
-        <f>D35+($Q35*1000)</f>
-        <v>148000</v>
+        <f>D39+($Q39*1000)</f>
+        <v>182000</v>
       </c>
       <c r="E40" t="s">
         <v>19</v>
       </c>
       <c r="F40" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G40">
-        <f t="shared" si="2"/>
-        <v>156000</v>
+        <f>G39+$Q39*1000</f>
+        <v>182000</v>
       </c>
       <c r="H40" t="s">
-        <v>19</v>
+        <v>57</v>
       </c>
       <c r="I40" t="s">
-        <v>42</v>
+        <v>63</v>
       </c>
       <c r="J40">
-        <f>J39+($S$2)</f>
-        <v>156000</v>
+        <f>J39+$Q39*1000</f>
+        <v>182000</v>
       </c>
       <c r="K40" t="s">
-        <v>31</v>
+        <v>57</v>
       </c>
       <c r="L40" t="s">
-        <v>39</v>
+        <v>63</v>
       </c>
       <c r="M40">
-        <f>M35+($Q35*1000)</f>
-        <v>148000</v>
+        <f>M39+($Q39*1000)</f>
+        <v>182000</v>
       </c>
       <c r="N40" t="s">
         <v>19</v>
       </c>
       <c r="O40" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="P40">
-        <f>P35+1</f>
-        <v>9</v>
+        <f>P39+1</f>
+        <v>11</v>
       </c>
       <c r="Q40">
-        <v>10</v>
+        <v>21</v>
       </c>
     </row>
     <row r="41" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A41">
+        <f t="shared" si="3"/>
+        <v>203000</v>
+      </c>
+      <c r="B41" t="s">
+        <v>19</v>
+      </c>
+      <c r="C41" t="s">
+        <v>44</v>
+      </c>
+      <c r="D41">
+        <f t="shared" si="4"/>
+        <v>203000</v>
+      </c>
+      <c r="E41" t="s">
+        <v>19</v>
+      </c>
+      <c r="F41" t="s">
+        <v>44</v>
+      </c>
+      <c r="G41">
+        <f t="shared" ref="G41:G44" si="6">G40+$Q40*1000</f>
+        <v>203000</v>
+      </c>
+      <c r="H41" t="s">
+        <v>57</v>
+      </c>
+      <c r="I41" t="s">
+        <v>63</v>
+      </c>
       <c r="J41">
-        <f>J40+1000</f>
-        <v>157000</v>
+        <f t="shared" ref="J41:J44" si="7">J40+$Q40*1000</f>
+        <v>203000</v>
       </c>
       <c r="K41" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="L41" t="s">
-        <v>38</v>
+        <v>45</v>
+      </c>
+      <c r="M41">
+        <f t="shared" si="5"/>
+        <v>203000</v>
+      </c>
+      <c r="N41" t="s">
+        <v>19</v>
+      </c>
+      <c r="O41" t="s">
+        <v>44</v>
+      </c>
+      <c r="P41">
+        <f t="shared" ref="P41:P44" si="8">P40+1</f>
+        <v>12</v>
+      </c>
+      <c r="Q41">
+        <v>4</v>
       </c>
     </row>
     <row r="42" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A42">
+        <f t="shared" si="3"/>
+        <v>207000</v>
+      </c>
+      <c r="B42" t="s">
+        <v>19</v>
+      </c>
+      <c r="C42" t="s">
+        <v>44</v>
+      </c>
+      <c r="D42">
+        <f t="shared" si="4"/>
+        <v>207000</v>
+      </c>
+      <c r="E42" t="s">
+        <v>19</v>
+      </c>
+      <c r="F42" t="s">
+        <v>44</v>
+      </c>
+      <c r="G42">
+        <f t="shared" si="6"/>
+        <v>207000</v>
+      </c>
+      <c r="H42" t="s">
+        <v>31</v>
+      </c>
+      <c r="I42" t="s">
+        <v>45</v>
+      </c>
       <c r="J42">
-        <f>J41+3000</f>
-        <v>160000</v>
+        <f t="shared" si="7"/>
+        <v>207000</v>
       </c>
       <c r="K42" t="s">
         <v>31</v>
       </c>
       <c r="L42" t="s">
-        <v>39</v>
+        <v>45</v>
+      </c>
+      <c r="M42">
+        <f t="shared" si="5"/>
+        <v>207000</v>
+      </c>
+      <c r="N42" t="s">
+        <v>19</v>
+      </c>
+      <c r="O42" t="s">
+        <v>44</v>
+      </c>
+      <c r="P42">
+        <f t="shared" si="8"/>
+        <v>13</v>
+      </c>
+      <c r="Q42">
+        <v>4</v>
       </c>
     </row>
     <row r="43" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A43">
-        <f>A40+($Q40*1000)</f>
-        <v>158000</v>
+        <f t="shared" si="3"/>
+        <v>211000</v>
       </c>
       <c r="B43" t="s">
         <v>19</v>
       </c>
       <c r="C43" t="s">
-        <v>63</v>
+        <v>46</v>
       </c>
       <c r="D43">
-        <f>D40+($Q40*1000)</f>
-        <v>158000</v>
+        <f t="shared" si="4"/>
+        <v>211000</v>
       </c>
       <c r="E43" t="s">
         <v>19</v>
       </c>
       <c r="F43" t="s">
-        <v>63</v>
+        <v>46</v>
       </c>
       <c r="G43">
-        <f>G40+Q40*1000</f>
-        <v>166000</v>
+        <f t="shared" si="6"/>
+        <v>211000</v>
       </c>
       <c r="H43" t="s">
         <v>31</v>
       </c>
       <c r="I43" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="J43">
-        <f>J42+6000</f>
-        <v>166000</v>
+        <f t="shared" si="7"/>
+        <v>211000</v>
       </c>
       <c r="K43" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="L43" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="M43">
-        <f>M40+($Q40*1000)</f>
-        <v>158000</v>
+        <f t="shared" si="5"/>
+        <v>211000</v>
       </c>
       <c r="N43" t="s">
         <v>19</v>
       </c>
       <c r="O43" t="s">
-        <v>63</v>
+        <v>46</v>
       </c>
       <c r="P43">
-        <f>P40+1</f>
-        <v>10</v>
+        <f t="shared" si="8"/>
+        <v>14</v>
       </c>
       <c r="Q43">
-        <v>6</v>
-      </c>
-      <c r="R43" t="s">
-        <v>44</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A44">
-        <f t="shared" ref="A44:A49" si="3">A43+($Q43*1000)</f>
-        <v>164000</v>
+        <f t="shared" si="3"/>
+        <v>213000</v>
       </c>
       <c r="B44" t="s">
         <v>19</v>
       </c>
       <c r="C44" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="D44">
-        <f t="shared" ref="D44:D49" si="4">D43+($Q43*1000)</f>
-        <v>164000</v>
+        <f t="shared" si="4"/>
+        <v>213000</v>
       </c>
       <c r="E44" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="F44" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="G44">
-        <f t="shared" ref="G44:G49" si="5">G43+$Q43*1000</f>
-        <v>172000</v>
+        <f t="shared" si="6"/>
+        <v>213000</v>
       </c>
       <c r="H44" t="s">
-        <v>59</v>
+        <v>31</v>
       </c>
       <c r="I44" t="s">
-        <v>72</v>
+        <v>32</v>
       </c>
       <c r="J44">
-        <f t="shared" ref="J44:J49" si="6">J43+$Q43*1000</f>
-        <v>172000</v>
+        <f t="shared" si="7"/>
+        <v>213000</v>
       </c>
       <c r="K44" t="s">
-        <v>59</v>
+        <v>31</v>
       </c>
       <c r="L44" t="s">
-        <v>70</v>
+        <v>33</v>
       </c>
       <c r="M44">
-        <f t="shared" ref="M44:M49" si="7">M43+($Q43*1000)</f>
-        <v>164000</v>
+        <f t="shared" si="5"/>
+        <v>213000</v>
       </c>
       <c r="N44" t="s">
         <v>19</v>
       </c>
       <c r="O44" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="P44">
-        <f>P43+1</f>
-        <v>11</v>
-      </c>
-      <c r="Q44">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="45" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A45">
-        <f t="shared" si="3"/>
-        <v>199000</v>
-      </c>
-      <c r="B45" t="s">
-        <v>19</v>
-      </c>
-      <c r="C45" t="s">
-        <v>46</v>
-      </c>
-      <c r="D45">
-        <f t="shared" si="4"/>
-        <v>199000</v>
-      </c>
-      <c r="E45" t="s">
-        <v>19</v>
-      </c>
-      <c r="F45" t="s">
-        <v>46</v>
-      </c>
-      <c r="G45">
-        <f t="shared" si="5"/>
-        <v>207000</v>
-      </c>
-      <c r="H45" t="s">
-        <v>61</v>
-      </c>
-      <c r="I45" t="s">
-        <v>71</v>
-      </c>
-      <c r="J45">
-        <f t="shared" si="6"/>
-        <v>207000</v>
-      </c>
-      <c r="K45" t="s">
-        <v>61</v>
-      </c>
-      <c r="L45" t="s">
-        <v>71</v>
-      </c>
-      <c r="M45">
-        <f t="shared" si="7"/>
-        <v>199000</v>
-      </c>
-      <c r="N45" t="s">
-        <v>19</v>
-      </c>
-      <c r="O45" t="s">
-        <v>46</v>
-      </c>
-      <c r="P45">
-        <f t="shared" ref="P45:P49" si="8">P44+1</f>
-        <v>12</v>
-      </c>
-      <c r="Q45">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="46" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A46">
-        <f t="shared" si="3"/>
-        <v>220000</v>
-      </c>
-      <c r="B46" t="s">
-        <v>19</v>
-      </c>
-      <c r="C46" t="s">
-        <v>47</v>
-      </c>
-      <c r="D46">
-        <f t="shared" si="4"/>
-        <v>220000</v>
-      </c>
-      <c r="E46" t="s">
-        <v>19</v>
-      </c>
-      <c r="F46" t="s">
-        <v>47</v>
-      </c>
-      <c r="G46">
-        <f t="shared" si="5"/>
-        <v>228000</v>
-      </c>
-      <c r="H46" t="s">
-        <v>61</v>
-      </c>
-      <c r="I46" t="s">
-        <v>71</v>
-      </c>
-      <c r="J46">
-        <f t="shared" si="6"/>
-        <v>228000</v>
-      </c>
-      <c r="K46" t="s">
-        <v>31</v>
-      </c>
-      <c r="L46" t="s">
-        <v>48</v>
-      </c>
-      <c r="M46">
-        <f t="shared" si="7"/>
-        <v>220000</v>
-      </c>
-      <c r="N46" t="s">
-        <v>19</v>
-      </c>
-      <c r="O46" t="s">
-        <v>47</v>
-      </c>
-      <c r="P46">
-        <f t="shared" si="8"/>
-        <v>13</v>
-      </c>
-      <c r="Q46">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="47" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A47">
-        <f t="shared" si="3"/>
-        <v>224000</v>
-      </c>
-      <c r="B47" t="s">
-        <v>19</v>
-      </c>
-      <c r="C47" t="s">
-        <v>47</v>
-      </c>
-      <c r="D47">
-        <f t="shared" si="4"/>
-        <v>224000</v>
-      </c>
-      <c r="E47" t="s">
-        <v>19</v>
-      </c>
-      <c r="F47" t="s">
-        <v>47</v>
-      </c>
-      <c r="G47">
-        <f t="shared" si="5"/>
-        <v>232000</v>
-      </c>
-      <c r="H47" t="s">
-        <v>31</v>
-      </c>
-      <c r="I47" t="s">
-        <v>48</v>
-      </c>
-      <c r="J47">
-        <f t="shared" si="6"/>
-        <v>232000</v>
-      </c>
-      <c r="K47" t="s">
-        <v>31</v>
-      </c>
-      <c r="L47" t="s">
-        <v>48</v>
-      </c>
-      <c r="M47">
-        <f t="shared" si="7"/>
-        <v>224000</v>
-      </c>
-      <c r="N47" t="s">
-        <v>19</v>
-      </c>
-      <c r="O47" t="s">
-        <v>47</v>
-      </c>
-      <c r="P47">
-        <f t="shared" si="8"/>
-        <v>14</v>
-      </c>
-      <c r="Q47">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="48" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A48">
-        <f t="shared" si="3"/>
-        <v>228000</v>
-      </c>
-      <c r="B48" t="s">
-        <v>19</v>
-      </c>
-      <c r="C48" t="s">
-        <v>49</v>
-      </c>
-      <c r="D48">
-        <f t="shared" si="4"/>
-        <v>228000</v>
-      </c>
-      <c r="E48" t="s">
-        <v>19</v>
-      </c>
-      <c r="F48" t="s">
-        <v>49</v>
-      </c>
-      <c r="G48">
-        <f t="shared" si="5"/>
-        <v>236000</v>
-      </c>
-      <c r="H48" t="s">
-        <v>31</v>
-      </c>
-      <c r="I48" t="s">
-        <v>50</v>
-      </c>
-      <c r="J48">
-        <f t="shared" si="6"/>
-        <v>236000</v>
-      </c>
-      <c r="K48" t="s">
-        <v>31</v>
-      </c>
-      <c r="L48" t="s">
-        <v>50</v>
-      </c>
-      <c r="M48">
-        <f t="shared" si="7"/>
-        <v>228000</v>
-      </c>
-      <c r="N48" t="s">
-        <v>19</v>
-      </c>
-      <c r="O48" t="s">
-        <v>49</v>
-      </c>
-      <c r="P48">
         <f t="shared" si="8"/>
         <v>15</v>
       </c>
-      <c r="Q48">
-        <v>2</v>
+      <c r="Q44">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="45" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="D45">
+        <f>D44+($S$2*(1-$R$2))</f>
+        <v>216950</v>
+      </c>
+      <c r="E45" t="s">
+        <v>19</v>
+      </c>
+      <c r="F45" t="s">
+        <v>49</v>
+      </c>
+      <c r="G45">
+        <f t="shared" ref="G45:G61" si="9">G44+($S$2)</f>
+        <v>217000</v>
+      </c>
+      <c r="H45" t="s">
+        <v>19</v>
+      </c>
+      <c r="I45" t="s">
+        <v>34</v>
+      </c>
+      <c r="J45">
+        <f>J44+($S$2*(1+$R$2))</f>
+        <v>217050</v>
+      </c>
+      <c r="K45" t="s">
+        <v>19</v>
+      </c>
+      <c r="L45" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="46" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="D46">
+        <f>D45+($S$2*(1-$R$2))</f>
+        <v>220900</v>
+      </c>
+      <c r="E46" t="s">
+        <v>31</v>
+      </c>
+      <c r="F46" t="s">
+        <v>48</v>
+      </c>
+      <c r="G46">
+        <f t="shared" si="9"/>
+        <v>221000</v>
+      </c>
+      <c r="H46" t="s">
+        <v>31</v>
+      </c>
+      <c r="I46" t="s">
+        <v>32</v>
+      </c>
+      <c r="J46">
+        <f t="shared" ref="J46:J65" si="10">J45+($S$2*(1+$R$2))</f>
+        <v>221100</v>
+      </c>
+      <c r="K46" t="s">
+        <v>31</v>
+      </c>
+      <c r="L46" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="47" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="D47">
+        <f t="shared" ref="D47:D68" si="11">D46+($S$2*(1-$R$2))</f>
+        <v>224850</v>
+      </c>
+      <c r="E47" t="s">
+        <v>19</v>
+      </c>
+      <c r="F47" t="s">
+        <v>49</v>
+      </c>
+      <c r="G47">
+        <f t="shared" si="9"/>
+        <v>225000</v>
+      </c>
+      <c r="H47" t="s">
+        <v>19</v>
+      </c>
+      <c r="I47" t="s">
+        <v>34</v>
+      </c>
+      <c r="J47">
+        <f t="shared" si="10"/>
+        <v>225150</v>
+      </c>
+      <c r="K47" t="s">
+        <v>19</v>
+      </c>
+      <c r="L47" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="48" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="D48">
+        <f t="shared" si="11"/>
+        <v>228800</v>
+      </c>
+      <c r="E48" t="s">
+        <v>31</v>
+      </c>
+      <c r="F48" t="s">
+        <v>48</v>
+      </c>
+      <c r="G48">
+        <f t="shared" si="9"/>
+        <v>229000</v>
+      </c>
+      <c r="H48" t="s">
+        <v>31</v>
+      </c>
+      <c r="I48" t="s">
+        <v>32</v>
+      </c>
+      <c r="J48">
+        <f t="shared" si="10"/>
+        <v>229200</v>
+      </c>
+      <c r="K48" t="s">
+        <v>31</v>
+      </c>
+      <c r="L48" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A49">
-        <f t="shared" si="3"/>
-        <v>230000</v>
-      </c>
-      <c r="B49" t="s">
-        <v>19</v>
-      </c>
-      <c r="C49" t="s">
-        <v>30</v>
-      </c>
       <c r="D49">
-        <f t="shared" si="4"/>
-        <v>230000</v>
+        <f t="shared" si="11"/>
+        <v>232750</v>
       </c>
       <c r="E49" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="F49" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G49">
-        <f t="shared" si="5"/>
-        <v>238000</v>
+        <f t="shared" si="9"/>
+        <v>233000</v>
       </c>
       <c r="H49" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="I49" t="s">
+        <v>34</v>
+      </c>
+      <c r="J49">
+        <f t="shared" si="10"/>
+        <v>233250</v>
+      </c>
+      <c r="K49" t="s">
+        <v>19</v>
+      </c>
+      <c r="L49" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="50" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A50">
+        <f>A44+(Q44*1000)-((G49-D50)*0.5)</f>
+        <v>238850</v>
+      </c>
+      <c r="B50" t="s">
+        <v>31</v>
+      </c>
+      <c r="C50" t="s">
+        <v>81</v>
+      </c>
+      <c r="D50">
+        <f t="shared" si="11"/>
+        <v>236700</v>
+      </c>
+      <c r="E50" t="s">
+        <v>31</v>
+      </c>
+      <c r="F50" t="s">
+        <v>48</v>
+      </c>
+      <c r="G50">
+        <f t="shared" si="9"/>
+        <v>237000</v>
+      </c>
+      <c r="H50" t="s">
+        <v>31</v>
+      </c>
+      <c r="I50" t="s">
         <v>32</v>
       </c>
-      <c r="J49">
-        <f t="shared" si="6"/>
-        <v>238000</v>
-      </c>
-      <c r="K49" t="s">
-        <v>31</v>
-      </c>
-      <c r="L49" t="s">
+      <c r="J50">
+        <f t="shared" si="10"/>
+        <v>237300</v>
+      </c>
+      <c r="K50" t="s">
+        <v>31</v>
+      </c>
+      <c r="L50" t="s">
         <v>33</v>
       </c>
-      <c r="M49">
-        <f t="shared" si="7"/>
-        <v>230000</v>
-      </c>
-      <c r="N49" t="s">
-        <v>19</v>
-      </c>
-      <c r="O49" t="s">
-        <v>30</v>
-      </c>
-      <c r="P49">
-        <f t="shared" si="8"/>
+      <c r="M50">
+        <f>M44+($Q44*1000)</f>
+        <v>237000</v>
+      </c>
+      <c r="N50" t="s">
+        <v>19</v>
+      </c>
+      <c r="O50" t="s">
+        <v>36</v>
+      </c>
+      <c r="P50">
+        <f>P44+1</f>
         <v>16</v>
       </c>
-      <c r="Q49">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="D50">
-        <f>D49+($S$2*(1-$R$2))</f>
-        <v>233950</v>
-      </c>
-      <c r="E50" t="s">
-        <v>19</v>
-      </c>
-      <c r="F50" t="s">
-        <v>52</v>
-      </c>
-      <c r="G50">
-        <f t="shared" ref="G50:G66" si="9">G49+($S$2)</f>
-        <v>242000</v>
-      </c>
-      <c r="H50" t="s">
-        <v>19</v>
-      </c>
-      <c r="I50" t="s">
-        <v>34</v>
-      </c>
-      <c r="J50">
-        <f>J49+($S$2*(1+$R$2))</f>
-        <v>242050</v>
-      </c>
-      <c r="K50" t="s">
-        <v>19</v>
-      </c>
-      <c r="L50" t="s">
-        <v>35</v>
+      <c r="Q50">
+        <v>28</v>
       </c>
     </row>
     <row r="51" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D51">
-        <f>D50+($S$2*(1-$R$2))</f>
-        <v>237900</v>
+        <f t="shared" si="11"/>
+        <v>240650</v>
       </c>
       <c r="E51" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="F51" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G51">
         <f t="shared" si="9"/>
-        <v>246000</v>
+        <v>241000</v>
       </c>
       <c r="H51" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="I51" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J51">
-        <f t="shared" ref="J51:J70" si="10">J50+($S$2*(1+$R$2))</f>
-        <v>246100</v>
+        <f t="shared" si="10"/>
+        <v>241350</v>
       </c>
       <c r="K51" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="L51" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="52" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D52">
-        <f t="shared" ref="D52:D73" si="11">D51+($S$2*(1-$R$2))</f>
-        <v>241850</v>
+        <f t="shared" si="11"/>
+        <v>244600</v>
       </c>
       <c r="E52" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="F52" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G52">
         <f t="shared" si="9"/>
-        <v>250000</v>
+        <v>245000</v>
       </c>
       <c r="H52" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="I52" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="J52">
         <f t="shared" si="10"/>
-        <v>250150</v>
+        <v>245400</v>
       </c>
       <c r="K52" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="L52" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="53" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A53">
+        <f>G44+($S$2*(1-$R$2*2))*10</f>
+        <v>252000</v>
+      </c>
+      <c r="B53" t="s">
+        <v>31</v>
+      </c>
+      <c r="C53" t="s">
+        <v>81</v>
+      </c>
       <c r="D53">
         <f t="shared" si="11"/>
-        <v>245800</v>
+        <v>248550</v>
       </c>
       <c r="E53" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="F53" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G53">
         <f t="shared" si="9"/>
-        <v>254000</v>
+        <v>249000</v>
       </c>
       <c r="H53" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="I53" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J53">
         <f t="shared" si="10"/>
-        <v>254200</v>
+        <v>249450</v>
       </c>
       <c r="K53" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="L53" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="54" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A54">
+        <f t="shared" ref="A54:A67" si="12">A53+($S$2*(1-$R$2*2))</f>
+        <v>255900</v>
+      </c>
+      <c r="B54" t="s">
+        <v>19</v>
+      </c>
+      <c r="C54" t="s">
+        <v>50</v>
+      </c>
       <c r="D54">
         <f t="shared" si="11"/>
-        <v>249750</v>
+        <v>252500</v>
       </c>
       <c r="E54" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="F54" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G54">
         <f t="shared" si="9"/>
-        <v>258000</v>
+        <v>253000</v>
       </c>
       <c r="H54" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="I54" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="J54">
         <f t="shared" si="10"/>
-        <v>258250</v>
+        <v>253500</v>
       </c>
       <c r="K54" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="L54" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="55" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A55">
-        <f>A49+(Q49*1000)-((G54-D55)*0.5)</f>
-        <v>251850</v>
+        <f t="shared" si="12"/>
+        <v>259800</v>
       </c>
       <c r="B55" t="s">
         <v>31</v>
       </c>
       <c r="C55" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="D55">
         <f t="shared" si="11"/>
-        <v>253700</v>
+        <v>256450</v>
       </c>
       <c r="E55" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="F55" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G55">
         <f t="shared" si="9"/>
-        <v>262000</v>
+        <v>257000</v>
       </c>
       <c r="H55" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="I55" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J55">
         <f t="shared" si="10"/>
-        <v>262300</v>
+        <v>257550</v>
       </c>
       <c r="K55" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="L55" t="s">
-        <v>33</v>
-      </c>
-      <c r="M55">
-        <f>M49+($Q49*1000)</f>
-        <v>254000</v>
-      </c>
-      <c r="N55" t="s">
-        <v>19</v>
-      </c>
-      <c r="O55" t="s">
-        <v>36</v>
-      </c>
-      <c r="P55">
-        <f>P49+1</f>
-        <v>17</v>
-      </c>
-      <c r="Q55">
-        <v>28</v>
+        <v>35</v>
       </c>
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A56">
+        <f t="shared" si="12"/>
+        <v>263700</v>
+      </c>
+      <c r="B56" t="s">
+        <v>19</v>
+      </c>
+      <c r="C56" t="s">
+        <v>50</v>
+      </c>
       <c r="D56">
         <f t="shared" si="11"/>
-        <v>257650</v>
+        <v>260400</v>
       </c>
       <c r="E56" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="F56" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G56">
         <f t="shared" si="9"/>
-        <v>266000</v>
+        <v>261000</v>
       </c>
       <c r="H56" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="I56" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="J56">
         <f t="shared" si="10"/>
-        <v>266350</v>
+        <v>261600</v>
       </c>
       <c r="K56" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="L56" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="57" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A57">
+        <f t="shared" si="12"/>
+        <v>267600</v>
+      </c>
+      <c r="B57" t="s">
+        <v>31</v>
+      </c>
+      <c r="C57" t="s">
+        <v>51</v>
+      </c>
       <c r="D57">
         <f t="shared" si="11"/>
-        <v>261600</v>
+        <v>264350</v>
       </c>
       <c r="E57" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="F57" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G57">
         <f t="shared" si="9"/>
-        <v>270000</v>
+        <v>265000</v>
       </c>
       <c r="H57" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="I57" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J57">
         <f t="shared" si="10"/>
-        <v>270400</v>
+        <v>265650</v>
       </c>
       <c r="K57" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="L57" t="s">
-        <v>33</v>
+        <v>35</v>
+      </c>
+      <c r="M57">
+        <f>M50+($Q50*1000)</f>
+        <v>265000</v>
+      </c>
+      <c r="N57" t="s">
+        <v>19</v>
+      </c>
+      <c r="O57" t="s">
+        <v>52</v>
+      </c>
+      <c r="P57">
+        <f>P50+1</f>
+        <v>17</v>
+      </c>
+      <c r="Q57">
+        <v>20</v>
       </c>
     </row>
     <row r="58" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A58">
-        <f>G49+($S$2*(1-$R$2*2))*10</f>
-        <v>277000</v>
+        <f t="shared" si="12"/>
+        <v>271500</v>
       </c>
       <c r="B58" t="s">
         <v>19</v>
       </c>
       <c r="C58" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D58">
         <f t="shared" si="11"/>
-        <v>265550</v>
+        <v>268300</v>
       </c>
       <c r="E58" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="F58" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G58">
         <f t="shared" si="9"/>
-        <v>274000</v>
+        <v>269000</v>
       </c>
       <c r="H58" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="I58" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="J58">
         <f t="shared" si="10"/>
-        <v>274450</v>
+        <v>269700</v>
       </c>
       <c r="K58" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="L58" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="59" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A59">
-        <f t="shared" ref="A59:A72" si="12">A58+($S$2*(1-$R$2*2))</f>
-        <v>280900</v>
+        <f t="shared" si="12"/>
+        <v>275400</v>
       </c>
       <c r="B59" t="s">
         <v>31</v>
       </c>
       <c r="C59" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D59">
         <f t="shared" si="11"/>
-        <v>269500</v>
+        <v>272250</v>
       </c>
       <c r="E59" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="F59" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G59">
         <f t="shared" si="9"/>
-        <v>278000</v>
+        <v>273000</v>
       </c>
       <c r="H59" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="I59" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J59">
         <f t="shared" si="10"/>
-        <v>278500</v>
+        <v>273750</v>
       </c>
       <c r="K59" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="L59" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="60" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A60">
         <f t="shared" si="12"/>
-        <v>284800</v>
+        <v>279300</v>
       </c>
       <c r="B60" t="s">
         <v>19</v>
       </c>
       <c r="C60" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D60">
         <f t="shared" si="11"/>
-        <v>273450</v>
+        <v>276200</v>
       </c>
       <c r="E60" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="F60" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G60">
         <f t="shared" si="9"/>
-        <v>282000</v>
+        <v>277000</v>
       </c>
       <c r="H60" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="I60" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="J60">
         <f t="shared" si="10"/>
-        <v>282550</v>
+        <v>277800</v>
       </c>
       <c r="K60" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="L60" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="61" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A61">
         <f t="shared" si="12"/>
-        <v>288700</v>
+        <v>283200</v>
       </c>
       <c r="B61" t="s">
         <v>31</v>
       </c>
       <c r="C61" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D61">
         <f t="shared" si="11"/>
-        <v>277400</v>
+        <v>280150</v>
       </c>
       <c r="E61" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="F61" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G61">
         <f t="shared" si="9"/>
-        <v>286000</v>
+        <v>281000</v>
       </c>
       <c r="H61" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="I61" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="J61">
         <f t="shared" si="10"/>
-        <v>286600</v>
+        <v>281850</v>
       </c>
       <c r="K61" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="L61" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="62" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A62">
         <f t="shared" si="12"/>
-        <v>292600</v>
+        <v>287100</v>
       </c>
       <c r="B62" t="s">
         <v>19</v>
       </c>
       <c r="C62" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D62">
         <f t="shared" si="11"/>
-        <v>281350</v>
+        <v>284100</v>
       </c>
       <c r="E62" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="F62" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G62">
-        <f t="shared" si="9"/>
-        <v>290000</v>
+        <f>G61+($S$2)</f>
+        <v>285000</v>
       </c>
       <c r="H62" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="I62" t="s">
-        <v>34</v>
+        <v>62</v>
       </c>
       <c r="J62">
         <f t="shared" si="10"/>
-        <v>290650</v>
+        <v>285900</v>
       </c>
       <c r="K62" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="L62" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="M62">
-        <f>M55+($Q55*1000)</f>
-        <v>282000</v>
+        <f>M57+($Q57*1000)</f>
+        <v>285000</v>
       </c>
       <c r="N62" t="s">
         <v>19</v>
       </c>
       <c r="O62" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="P62">
-        <f>P55+1</f>
+        <f>P57+1</f>
         <v>18</v>
       </c>
       <c r="Q62">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="63" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A63">
         <f t="shared" si="12"/>
-        <v>296500</v>
+        <v>291000</v>
       </c>
       <c r="B63" t="s">
         <v>31</v>
       </c>
       <c r="C63" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D63">
         <f t="shared" si="11"/>
-        <v>285300</v>
+        <v>288050</v>
       </c>
       <c r="E63" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="F63" t="s">
-        <v>51</v>
-      </c>
-      <c r="G63">
-        <f t="shared" si="9"/>
-        <v>294000</v>
-      </c>
-      <c r="H63" t="s">
-        <v>31</v>
-      </c>
-      <c r="I63" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="J63">
         <f t="shared" si="10"/>
-        <v>294700</v>
+        <v>289950</v>
       </c>
       <c r="K63" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="L63" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="64" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A64">
         <f t="shared" si="12"/>
-        <v>300400</v>
+        <v>294900</v>
       </c>
       <c r="B64" t="s">
         <v>19</v>
       </c>
       <c r="C64" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D64">
         <f t="shared" si="11"/>
-        <v>289250</v>
+        <v>292000</v>
       </c>
       <c r="E64" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="F64" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G64">
-        <f t="shared" si="9"/>
-        <v>298000</v>
+        <f>G62+$Q62*1000</f>
+        <v>295000</v>
       </c>
       <c r="H64" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="I64" t="s">
-        <v>34</v>
+        <v>62</v>
       </c>
       <c r="J64">
         <f t="shared" si="10"/>
-        <v>298750</v>
+        <v>294000</v>
       </c>
       <c r="K64" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="L64" t="s">
-        <v>35</v>
+        <v>33</v>
+      </c>
+      <c r="M64">
+        <f>M62+($Q62*1000)</f>
+        <v>295000</v>
+      </c>
+      <c r="N64" t="s">
+        <v>19</v>
+      </c>
+      <c r="O64" t="s">
+        <v>54</v>
+      </c>
+      <c r="P64">
+        <f>P62+1</f>
+        <v>19</v>
+      </c>
+      <c r="Q64">
+        <v>15</v>
       </c>
     </row>
     <row r="65" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A65">
         <f t="shared" si="12"/>
-        <v>304300</v>
+        <v>298800</v>
       </c>
       <c r="B65" t="s">
         <v>31</v>
       </c>
       <c r="C65" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D65">
         <f t="shared" si="11"/>
-        <v>293200</v>
+        <v>295950</v>
       </c>
       <c r="E65" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="F65" t="s">
-        <v>51</v>
-      </c>
-      <c r="G65">
-        <f t="shared" si="9"/>
-        <v>302000</v>
-      </c>
-      <c r="H65" t="s">
-        <v>31</v>
-      </c>
-      <c r="I65" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="J65">
         <f t="shared" si="10"/>
-        <v>302800</v>
+        <v>298050</v>
       </c>
       <c r="K65" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="L65" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
     </row>
     <row r="66" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A66">
         <f t="shared" si="12"/>
-        <v>308200</v>
+        <v>302700</v>
       </c>
       <c r="B66" t="s">
         <v>19</v>
       </c>
       <c r="C66" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="D66">
         <f t="shared" si="11"/>
-        <v>297150</v>
+        <v>299900</v>
       </c>
       <c r="E66" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="F66" t="s">
-        <v>52</v>
-      </c>
-      <c r="G66">
-        <f t="shared" si="9"/>
-        <v>306000</v>
-      </c>
-      <c r="H66" t="s">
-        <v>19</v>
-      </c>
-      <c r="I66" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="J66">
-        <f t="shared" si="10"/>
-        <v>306850</v>
+        <f>J65+($S$2*(1+$R$2))</f>
+        <v>302100</v>
       </c>
       <c r="K66" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="L66" t="s">
-        <v>35</v>
+        <v>62</v>
       </c>
     </row>
     <row r="67" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A67">
         <f t="shared" si="12"/>
-        <v>312100</v>
+        <v>306600</v>
       </c>
       <c r="B67" t="s">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="C67" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="D67">
         <f t="shared" si="11"/>
-        <v>301100</v>
+        <v>303850</v>
       </c>
       <c r="E67" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="F67" t="s">
-        <v>51</v>
-      </c>
-      <c r="G67">
-        <f>G66+($S$2)</f>
-        <v>310000</v>
-      </c>
-      <c r="H67" t="s">
-        <v>59</v>
-      </c>
-      <c r="I67" t="s">
-        <v>70</v>
-      </c>
-      <c r="J67">
-        <f t="shared" si="10"/>
-        <v>310900</v>
-      </c>
-      <c r="K67" t="s">
-        <v>31</v>
-      </c>
-      <c r="L67" t="s">
-        <v>33</v>
-      </c>
-      <c r="M67">
-        <f>M62+($Q62*1000)</f>
-        <v>302000</v>
-      </c>
-      <c r="N67" t="s">
-        <v>19</v>
-      </c>
-      <c r="O67" t="s">
-        <v>41</v>
-      </c>
-      <c r="P67">
-        <f>P62+1</f>
-        <v>19</v>
-      </c>
-      <c r="Q67">
-        <v>10</v>
+        <v>49</v>
       </c>
     </row>
     <row r="68" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A68">
-        <f t="shared" si="12"/>
-        <v>316000</v>
-      </c>
-      <c r="B68" t="s">
-        <v>19</v>
-      </c>
-      <c r="C68" t="s">
-        <v>53</v>
-      </c>
       <c r="D68">
         <f t="shared" si="11"/>
-        <v>305050</v>
+        <v>307800</v>
       </c>
       <c r="E68" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="F68" t="s">
-        <v>52</v>
-      </c>
-      <c r="J68">
-        <f t="shared" si="10"/>
-        <v>314950</v>
-      </c>
-      <c r="K68" t="s">
-        <v>19</v>
-      </c>
-      <c r="L68" t="s">
-        <v>35</v>
+        <v>62</v>
       </c>
     </row>
     <row r="69" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A69">
-        <f t="shared" si="12"/>
-        <v>319900</v>
+        <f>$M69</f>
+        <v>310000</v>
       </c>
       <c r="B69" t="s">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="C69" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="D69">
-        <f t="shared" si="11"/>
-        <v>309000</v>
+        <f>$M69</f>
+        <v>310000</v>
       </c>
       <c r="E69" t="s">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="F69" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="G69">
-        <f>G67+$Q67*1000</f>
-        <v>320000</v>
+        <f>$M69</f>
+        <v>310000</v>
       </c>
       <c r="H69" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="I69" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="J69">
-        <f t="shared" si="10"/>
-        <v>319000</v>
+        <f>$M69</f>
+        <v>310000</v>
       </c>
       <c r="K69" t="s">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="L69" t="s">
-        <v>33</v>
+        <v>62</v>
       </c>
       <c r="M69">
-        <f>M67+($Q67*1000)</f>
-        <v>312000</v>
+        <f>M64+($Q64*1000)</f>
+        <v>310000</v>
       </c>
       <c r="N69" t="s">
         <v>19</v>
       </c>
       <c r="O69" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="P69">
-        <f>P67+1</f>
+        <f>P64+1</f>
         <v>20</v>
       </c>
       <c r="Q69">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="70" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A70">
-        <f t="shared" si="12"/>
-        <v>323800</v>
+        <f>$M70</f>
+        <v>350000</v>
       </c>
       <c r="B70" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="C70" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="D70">
-        <f t="shared" si="11"/>
-        <v>312950</v>
+        <f>$M70</f>
+        <v>350000</v>
       </c>
       <c r="E70" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="F70" t="s">
-        <v>52</v>
+        <v>62</v>
+      </c>
+      <c r="G70">
+        <f>$M70</f>
+        <v>350000</v>
+      </c>
+      <c r="H70" t="s">
+        <v>57</v>
+      </c>
+      <c r="I70" t="s">
+        <v>63</v>
       </c>
       <c r="J70">
-        <f t="shared" si="10"/>
-        <v>323050</v>
+        <f>$M70</f>
+        <v>350000</v>
       </c>
       <c r="K70" t="s">
-        <v>19</v>
+        <v>57</v>
       </c>
       <c r="L70" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A71">
-        <f t="shared" si="12"/>
-        <v>327700</v>
-      </c>
-      <c r="B71" t="s">
-        <v>31</v>
-      </c>
-      <c r="C71" t="s">
-        <v>58</v>
-      </c>
-      <c r="D71">
-        <f t="shared" si="11"/>
-        <v>316900</v>
-      </c>
-      <c r="E71" t="s">
-        <v>31</v>
-      </c>
-      <c r="F71" t="s">
-        <v>51</v>
-      </c>
-      <c r="J71">
-        <f>J70+($S$2*(1+$R$2))</f>
-        <v>327100</v>
-      </c>
-      <c r="K71" t="s">
-        <v>59</v>
-      </c>
-      <c r="L71" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A72">
-        <f t="shared" si="12"/>
-        <v>331600</v>
-      </c>
-      <c r="B72" t="s">
-        <v>59</v>
-      </c>
-      <c r="C72" t="s">
-        <v>70</v>
-      </c>
-      <c r="D72">
-        <f t="shared" si="11"/>
-        <v>320850</v>
-      </c>
-      <c r="E72" t="s">
-        <v>19</v>
-      </c>
-      <c r="F72" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="D73">
-        <f t="shared" si="11"/>
-        <v>324800</v>
-      </c>
-      <c r="E73" t="s">
-        <v>59</v>
-      </c>
-      <c r="F73" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A74">
-        <f>$M74</f>
-        <v>327000</v>
-      </c>
-      <c r="B74" t="s">
-        <v>59</v>
-      </c>
-      <c r="C74" t="s">
-        <v>70</v>
-      </c>
-      <c r="D74">
-        <f>$M74</f>
-        <v>327000</v>
-      </c>
-      <c r="E74" t="s">
-        <v>59</v>
-      </c>
-      <c r="F74" t="s">
-        <v>70</v>
-      </c>
-      <c r="G74">
-        <f>$M74</f>
-        <v>327000</v>
-      </c>
-      <c r="H74" t="s">
-        <v>61</v>
-      </c>
-      <c r="I74" t="s">
-        <v>71</v>
-      </c>
-      <c r="J74">
-        <f>$M74</f>
-        <v>327000</v>
-      </c>
-      <c r="K74" t="s">
-        <v>59</v>
-      </c>
-      <c r="L74" t="s">
-        <v>70</v>
-      </c>
-      <c r="M74">
+        <v>63</v>
+      </c>
+      <c r="M70">
         <f>M69+($Q69*1000)</f>
-        <v>327000</v>
-      </c>
-      <c r="N74" t="s">
-        <v>19</v>
-      </c>
-      <c r="O74" t="s">
-        <v>60</v>
-      </c>
-      <c r="P74">
+        <v>350000</v>
+      </c>
+      <c r="N70" t="s">
+        <v>19</v>
+      </c>
+      <c r="O70" t="s">
+        <v>40</v>
+      </c>
+      <c r="P70">
         <f>P69+1</f>
         <v>21</v>
       </c>
+      <c r="Q70">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="71" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="D71">
+        <f>((D72-D70)/2)+D70</f>
+        <v>352500</v>
+      </c>
+      <c r="E71" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="72" spans="1:17" ht="34" x14ac:dyDescent="0.2">
+      <c r="A72">
+        <f>$M72</f>
+        <v>355000</v>
+      </c>
+      <c r="B72" t="s">
+        <v>57</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="D72">
+        <f>$M72</f>
+        <v>355000</v>
+      </c>
+      <c r="E72" t="s">
+        <v>57</v>
+      </c>
+      <c r="F72" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="G72">
+        <f>$M72</f>
+        <v>355000</v>
+      </c>
+      <c r="H72" t="s">
+        <v>57</v>
+      </c>
+      <c r="I72" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="J72">
+        <f>$M72</f>
+        <v>355000</v>
+      </c>
+      <c r="K72" t="s">
+        <v>57</v>
+      </c>
+      <c r="L72" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="M72">
+        <f>M70+($Q70*1000)</f>
+        <v>355000</v>
+      </c>
+      <c r="N72" t="s">
+        <v>19</v>
+      </c>
+      <c r="O72" t="s">
+        <v>62</v>
+      </c>
+      <c r="P72">
+        <f>P70+1</f>
+        <v>22</v>
+      </c>
+      <c r="Q72">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="73" spans="1:17" ht="34" x14ac:dyDescent="0.2">
+      <c r="A73">
+        <f>A72+($Q72*1000)</f>
+        <v>565000</v>
+      </c>
+      <c r="B73" t="s">
+        <v>19</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="D73">
+        <f>D72+($Q72*1000)</f>
+        <v>565000</v>
+      </c>
+      <c r="E73" t="s">
+        <v>19</v>
+      </c>
+      <c r="F73" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="G73">
+        <f>G72+($Q72*1000)</f>
+        <v>565000</v>
+      </c>
+      <c r="H73" t="s">
+        <v>19</v>
+      </c>
+      <c r="I73" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="J73">
+        <f>J72+($Q72*1000)</f>
+        <v>565000</v>
+      </c>
+      <c r="K73" t="s">
+        <v>19</v>
+      </c>
+      <c r="L73" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="M73">
+        <f>M72+($Q72*1000)</f>
+        <v>565000</v>
+      </c>
+      <c r="N73" t="s">
+        <v>19</v>
+      </c>
+      <c r="O73" t="s">
+        <v>62</v>
+      </c>
+      <c r="P73">
+        <f>P72+1</f>
+        <v>23</v>
+      </c>
+      <c r="Q73">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="74" spans="1:17" ht="68" x14ac:dyDescent="0.2">
+      <c r="A74">
+        <f>A73+($Q73*1000)</f>
+        <v>775000</v>
+      </c>
+      <c r="B74" t="s">
+        <v>60</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D74">
+        <f>D73+($Q73*1000)</f>
+        <v>775000</v>
+      </c>
+      <c r="E74" t="s">
+        <v>60</v>
+      </c>
+      <c r="F74" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="G74">
+        <f>G73+($Q73*1000)</f>
+        <v>775000</v>
+      </c>
+      <c r="H74" t="s">
+        <v>60</v>
+      </c>
+      <c r="I74" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="J74">
+        <f>J73+($Q73*1000)</f>
+        <v>775000</v>
+      </c>
+      <c r="K74" t="s">
+        <v>60</v>
+      </c>
+      <c r="L74" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="M74">
+        <f>M73+($Q73*1000)</f>
+        <v>775000</v>
+      </c>
+      <c r="N74" t="s">
+        <v>60</v>
+      </c>
+      <c r="O74" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="P74">
+        <f>P73+1</f>
+        <v>24</v>
+      </c>
       <c r="Q74">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A83">
-        <f>$M83</f>
-        <v>367000</v>
-      </c>
-      <c r="B83" t="s">
-        <v>59</v>
-      </c>
-      <c r="C83" t="s">
-        <v>70</v>
-      </c>
-      <c r="D83">
-        <f>$M83</f>
-        <v>367000</v>
-      </c>
-      <c r="E83" t="s">
-        <v>59</v>
-      </c>
-      <c r="F83" t="s">
-        <v>70</v>
-      </c>
-      <c r="G83">
-        <f>$M83</f>
-        <v>367000</v>
-      </c>
-      <c r="H83" t="s">
-        <v>61</v>
-      </c>
-      <c r="I83" t="s">
-        <v>71</v>
-      </c>
-      <c r="J83">
-        <f>$M83</f>
-        <v>367000</v>
-      </c>
-      <c r="K83" t="s">
-        <v>61</v>
-      </c>
-      <c r="L83" t="s">
-        <v>71</v>
-      </c>
-      <c r="M83">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="75" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A75">
+        <f>A74+($Q74*1000)</f>
+        <v>795000</v>
+      </c>
+      <c r="B75" t="s">
+        <v>19</v>
+      </c>
+      <c r="C75" t="s">
+        <v>78</v>
+      </c>
+      <c r="D75">
+        <f>D74+($Q74*1000)</f>
+        <v>795000</v>
+      </c>
+      <c r="E75" t="s">
+        <v>19</v>
+      </c>
+      <c r="F75" t="s">
+        <v>78</v>
+      </c>
+      <c r="G75">
+        <f>G74+($Q74*1000)</f>
+        <v>795000</v>
+      </c>
+      <c r="H75" t="s">
+        <v>19</v>
+      </c>
+      <c r="I75" t="s">
+        <v>78</v>
+      </c>
+      <c r="J75">
+        <f>J74+($Q74*1000)</f>
+        <v>795000</v>
+      </c>
+      <c r="K75" t="s">
+        <v>19</v>
+      </c>
+      <c r="L75" t="s">
+        <v>78</v>
+      </c>
+      <c r="M75">
         <f>M74+($Q74*1000)</f>
-        <v>367000</v>
-      </c>
-      <c r="N83" t="s">
-        <v>19</v>
-      </c>
-      <c r="O83" t="s">
-        <v>43</v>
-      </c>
-      <c r="P83">
+        <v>795000</v>
+      </c>
+      <c r="N75" t="s">
+        <v>19</v>
+      </c>
+      <c r="O75" t="s">
+        <v>78</v>
+      </c>
+      <c r="P75">
         <f>P74+1</f>
-        <v>22</v>
-      </c>
-      <c r="Q83">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="D84">
-        <f>((D85-D83)/2)+D83</f>
-        <v>369500</v>
-      </c>
-      <c r="E84" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A85">
-        <f>$M85</f>
-        <v>372000</v>
-      </c>
-      <c r="B85" t="s">
-        <v>61</v>
-      </c>
-      <c r="C85" t="s">
-        <v>71</v>
-      </c>
-      <c r="D85">
-        <f>$M85</f>
-        <v>372000</v>
-      </c>
-      <c r="E85" t="s">
-        <v>61</v>
-      </c>
-      <c r="F85" t="s">
-        <v>71</v>
-      </c>
-      <c r="G85">
-        <f>$M85</f>
-        <v>372000</v>
-      </c>
-      <c r="H85" t="s">
-        <v>61</v>
-      </c>
-      <c r="I85" t="s">
-        <v>71</v>
-      </c>
-      <c r="J85">
-        <f>$M85</f>
-        <v>372000</v>
-      </c>
-      <c r="K85" t="s">
-        <v>61</v>
-      </c>
-      <c r="L85" t="s">
-        <v>71</v>
-      </c>
-      <c r="M85">
-        <f>M83+($Q83*1000)</f>
-        <v>372000</v>
-      </c>
-      <c r="N85" t="s">
-        <v>19</v>
-      </c>
-      <c r="O85" t="s">
-        <v>66</v>
-      </c>
-      <c r="P85">
-        <f>P83+1</f>
-        <v>23</v>
-      </c>
-      <c r="Q85">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A86">
-        <f>A85+($Q85*1000)</f>
-        <v>582000</v>
-      </c>
-      <c r="B86" t="s">
-        <v>19</v>
-      </c>
-      <c r="C86" t="s">
-        <v>67</v>
-      </c>
-      <c r="D86">
-        <f>D85+($Q85*1000)</f>
-        <v>582000</v>
-      </c>
-      <c r="E86" t="s">
-        <v>19</v>
-      </c>
-      <c r="F86" t="s">
-        <v>67</v>
-      </c>
-      <c r="G86">
-        <f>G85+($Q85*1000)</f>
-        <v>582000</v>
-      </c>
-      <c r="H86" t="s">
-        <v>19</v>
-      </c>
-      <c r="I86" t="s">
-        <v>67</v>
-      </c>
-      <c r="J86">
-        <f>J85+($Q85*1000)</f>
-        <v>582000</v>
-      </c>
-      <c r="K86" t="s">
-        <v>19</v>
-      </c>
-      <c r="L86" t="s">
-        <v>67</v>
-      </c>
-      <c r="M86">
-        <f>M85+($Q85*1000)</f>
-        <v>582000</v>
-      </c>
-      <c r="N86" t="s">
-        <v>19</v>
-      </c>
-      <c r="O86" t="s">
-        <v>67</v>
-      </c>
-      <c r="P86">
-        <f>P85+1</f>
-        <v>24</v>
-      </c>
-      <c r="Q86">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A87">
-        <f>A86+($Q86*1000)</f>
-        <v>792000</v>
-      </c>
-      <c r="B87" t="s">
-        <v>68</v>
-      </c>
-      <c r="C87" t="s">
-        <v>65</v>
-      </c>
-      <c r="D87">
-        <f>D86+($Q86*1000)</f>
-        <v>792000</v>
-      </c>
-      <c r="E87" t="s">
-        <v>68</v>
-      </c>
-      <c r="F87" t="s">
-        <v>65</v>
-      </c>
-      <c r="G87">
-        <f>G86+($Q86*1000)</f>
-        <v>792000</v>
-      </c>
-      <c r="H87" t="s">
-        <v>68</v>
-      </c>
-      <c r="I87" t="s">
-        <v>65</v>
-      </c>
-      <c r="J87">
-        <f>J86+($Q86*1000)</f>
-        <v>792000</v>
-      </c>
-      <c r="K87" t="s">
-        <v>68</v>
-      </c>
-      <c r="L87" t="s">
-        <v>65</v>
-      </c>
-      <c r="M87">
-        <f>M86+($Q86*1000)</f>
-        <v>792000</v>
-      </c>
-      <c r="N87" t="s">
-        <v>68</v>
-      </c>
-      <c r="O87" t="s">
-        <v>65</v>
-      </c>
-      <c r="P87">
-        <f>P86+1</f>
         <v>25</v>
       </c>
-      <c r="Q87">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A88">
-        <f>A87+($Q87*1000)</f>
-        <v>812000</v>
-      </c>
-      <c r="B88" t="s">
-        <v>19</v>
-      </c>
-      <c r="C88" t="s">
-        <v>64</v>
-      </c>
-      <c r="D88">
-        <f>D87+($Q87*1000)</f>
-        <v>812000</v>
-      </c>
-      <c r="E88" t="s">
-        <v>19</v>
-      </c>
-      <c r="F88" t="s">
-        <v>64</v>
-      </c>
-      <c r="G88">
-        <f>G87+($Q87*1000)</f>
-        <v>812000</v>
-      </c>
-      <c r="H88" t="s">
-        <v>19</v>
-      </c>
-      <c r="I88" t="s">
-        <v>64</v>
-      </c>
-      <c r="J88">
-        <f>J87+($Q87*1000)</f>
-        <v>812000</v>
-      </c>
-      <c r="K88" t="s">
-        <v>19</v>
-      </c>
-      <c r="L88" t="s">
-        <v>64</v>
-      </c>
-      <c r="M88">
-        <f>M87+($Q87*1000)</f>
-        <v>812000</v>
-      </c>
-      <c r="N88" t="s">
-        <v>19</v>
-      </c>
-      <c r="O88" t="s">
-        <v>64</v>
-      </c>
-      <c r="P88">
-        <f>P87+1</f>
-        <v>26</v>
-      </c>
-      <c r="Q88">
+      <c r="Q75">
         <v>10000</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A1:XFD1048576">
+  <conditionalFormatting sqref="A1:XFD28 J29:L31 A29:I33 M29:XFD33 A34:XFD1048576 K32:L33">
     <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="bacon">
       <formula>NOT(ISERROR(SEARCH("bacon",A1)))</formula>
     </cfRule>

--- a/onsets_edit.xlsx
+++ b/onsets_edit.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10419"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10503"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/brandonwoosnyder/Dropbox/docs-d/00_UCI_2025-2026/02_UCI_Winter_2026/Independent Study Rajna - Music 299/Constrained_PhoneGuide_Score/ScreenTimeScore/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3386BBCA-04B7-D344-A5CC-AE710CBEC174}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB062B13-947F-3A4B-B920-48B0AD36A76D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-2160" yWindow="-23220" windowWidth="43080" windowHeight="19580" xr2:uid="{656903FE-55D6-334E-8317-D02588440573}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{656903FE-55D6-334E-8317-D02588440573}"/>
   </bookViews>
   <sheets>
     <sheet name="onsets" sheetId="1" r:id="rId1"/>
@@ -4046,13 +4046,13 @@
         <v>22</v>
       </c>
       <c r="Q72">
-        <v>210</v>
+        <v>60</v>
       </c>
     </row>
     <row r="73" spans="1:17" ht="34" x14ac:dyDescent="0.2">
       <c r="A73">
         <f>A72+($Q72*1000)</f>
-        <v>565000</v>
+        <v>415000</v>
       </c>
       <c r="B73" t="s">
         <v>19</v>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="D73">
         <f>D72+($Q72*1000)</f>
-        <v>565000</v>
+        <v>415000</v>
       </c>
       <c r="E73" t="s">
         <v>19</v>
@@ -4072,7 +4072,7 @@
       </c>
       <c r="G73">
         <f>G72+($Q72*1000)</f>
-        <v>565000</v>
+        <v>415000</v>
       </c>
       <c r="H73" t="s">
         <v>19</v>
@@ -4082,7 +4082,7 @@
       </c>
       <c r="J73">
         <f>J72+($Q72*1000)</f>
-        <v>565000</v>
+        <v>415000</v>
       </c>
       <c r="K73" t="s">
         <v>19</v>
@@ -4092,7 +4092,7 @@
       </c>
       <c r="M73">
         <f>M72+($Q72*1000)</f>
-        <v>565000</v>
+        <v>415000</v>
       </c>
       <c r="N73" t="s">
         <v>19</v>
@@ -4108,10 +4108,10 @@
         <v>210</v>
       </c>
     </row>
-    <row r="74" spans="1:17" ht="68" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:17" ht="34" x14ac:dyDescent="0.2">
       <c r="A74">
         <f>A73+($Q73*1000)</f>
-        <v>775000</v>
+        <v>625000</v>
       </c>
       <c r="B74" t="s">
         <v>60</v>
@@ -4121,7 +4121,7 @@
       </c>
       <c r="D74">
         <f>D73+($Q73*1000)</f>
-        <v>775000</v>
+        <v>625000</v>
       </c>
       <c r="E74" t="s">
         <v>60</v>
@@ -4131,7 +4131,7 @@
       </c>
       <c r="G74">
         <f>G73+($Q73*1000)</f>
-        <v>775000</v>
+        <v>625000</v>
       </c>
       <c r="H74" t="s">
         <v>60</v>
@@ -4141,7 +4141,7 @@
       </c>
       <c r="J74">
         <f>J73+($Q73*1000)</f>
-        <v>775000</v>
+        <v>625000</v>
       </c>
       <c r="K74" t="s">
         <v>60</v>
@@ -4151,7 +4151,7 @@
       </c>
       <c r="M74">
         <f>M73+($Q73*1000)</f>
-        <v>775000</v>
+        <v>625000</v>
       </c>
       <c r="N74" t="s">
         <v>60</v>
@@ -4170,7 +4170,7 @@
     <row r="75" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A75">
         <f>A74+($Q74*1000)</f>
-        <v>795000</v>
+        <v>645000</v>
       </c>
       <c r="B75" t="s">
         <v>19</v>
@@ -4180,7 +4180,7 @@
       </c>
       <c r="D75">
         <f>D74+($Q74*1000)</f>
-        <v>795000</v>
+        <v>645000</v>
       </c>
       <c r="E75" t="s">
         <v>19</v>
@@ -4190,7 +4190,7 @@
       </c>
       <c r="G75">
         <f>G74+($Q74*1000)</f>
-        <v>795000</v>
+        <v>645000</v>
       </c>
       <c r="H75" t="s">
         <v>19</v>
@@ -4200,7 +4200,7 @@
       </c>
       <c r="J75">
         <f>J74+($Q74*1000)</f>
-        <v>795000</v>
+        <v>645000</v>
       </c>
       <c r="K75" t="s">
         <v>19</v>
@@ -4210,7 +4210,7 @@
       </c>
       <c r="M75">
         <f>M74+($Q74*1000)</f>
-        <v>795000</v>
+        <v>645000</v>
       </c>
       <c r="N75" t="s">
         <v>19</v>
@@ -4227,7 +4227,7 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A1:XFD28 J29:L31 A29:I33 M29:XFD33 A34:XFD1048576 K32:L33">
+  <conditionalFormatting sqref="A1:XFD28 J29:L31 A29:I33 M29:XFD33 K32:L33 A34:XFD1048576">
     <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="bacon">
       <formula>NOT(ISERROR(SEARCH("bacon",A1)))</formula>
     </cfRule>

--- a/onsets_edit.xlsx
+++ b/onsets_edit.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10503"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10510"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/brandonwoosnyder/Dropbox/docs-d/00_UCI_2025-2026/02_UCI_Winter_2026/Independent Study Rajna - Music 299/Constrained_PhoneGuide_Score/ScreenTimeScore/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB062B13-947F-3A4B-B920-48B0AD36A76D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07FF8F69-5DAB-8B42-A3E5-F031907A74A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{656903FE-55D6-334E-8317-D02588440573}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="563" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="563" uniqueCount="85">
   <si>
     <t>onset_ms_1</t>
   </si>
@@ -287,6 +287,10 @@
   </si>
   <si>
     <t>Phone Up (3")</t>
+  </si>
+  <si>
+    <t>Phone Down
+Tacet 6"</t>
   </si>
 </sst>
 </file>
@@ -1828,7 +1832,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:19" ht="34" x14ac:dyDescent="0.2">
       <c r="A14">
         <f>A13+($Q13*1000)</f>
         <v>50000</v>
@@ -1836,8 +1840,8 @@
       <c r="B14" t="s">
         <v>19</v>
       </c>
-      <c r="C14" t="s">
-        <v>59</v>
+      <c r="C14" s="1" t="s">
+        <v>84</v>
       </c>
       <c r="D14">
         <f>D13+($Q13*1000)</f>
@@ -1846,8 +1850,8 @@
       <c r="E14" t="s">
         <v>19</v>
       </c>
-      <c r="F14" t="s">
-        <v>59</v>
+      <c r="F14" s="1" t="s">
+        <v>84</v>
       </c>
       <c r="G14">
         <f>G13+($Q13*1000)</f>
@@ -1856,8 +1860,8 @@
       <c r="H14" t="s">
         <v>19</v>
       </c>
-      <c r="I14" t="s">
-        <v>59</v>
+      <c r="I14" s="1" t="s">
+        <v>84</v>
       </c>
       <c r="J14">
         <f>J13+($Q13*1000)</f>
@@ -1866,8 +1870,8 @@
       <c r="K14" t="s">
         <v>19</v>
       </c>
-      <c r="L14" t="s">
-        <v>59</v>
+      <c r="L14" s="1" t="s">
+        <v>84</v>
       </c>
       <c r="M14">
         <f>M13+($Q13*1000)</f>
@@ -1876,8 +1880,8 @@
       <c r="N14" t="s">
         <v>19</v>
       </c>
-      <c r="O14" t="s">
-        <v>59</v>
+      <c r="O14" s="1" t="s">
+        <v>84</v>
       </c>
       <c r="P14">
         <f>P13+1</f>
@@ -4227,7 +4231,7 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A1:XFD28 J29:L31 A29:I33 M29:XFD33 K32:L33 A34:XFD1048576">
+  <conditionalFormatting sqref="J29:L31 A29:I33 M29:XFD33 K32:L33 A34:XFD1048576 A1:XFD28">
     <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="bacon">
       <formula>NOT(ISERROR(SEARCH("bacon",A1)))</formula>
     </cfRule>
